--- a/delay_pdf/11be/fix_nsta30_CwdsxQSRCxPSRC_sweep_onoff/param_p99_heatmap_1Mbps.xlsx
+++ b/delay_pdf/11be/fix_nsta30_CwdsxQSRCxPSRC_sweep_onoff/param_p99_heatmap_1Mbps.xlsx
@@ -1143,13 +1143,13 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>16682</v>
+        <v>21858</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>13448</v>
+        <v>15702</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>8782</v>
+        <v>9428</v>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
@@ -1157,13 +1157,13 @@
         </is>
       </c>
       <c r="G5" s="6" t="n">
-        <v>16682</v>
+        <v>21858</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>13128</v>
+        <v>16678</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>8852</v>
+        <v>9312</v>
       </c>
     </row>
     <row r="6">
@@ -1173,13 +1173,13 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>16802</v>
+        <v>19668</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>11378</v>
+        <v>14322</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>8732</v>
+        <v>10482</v>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
@@ -1187,13 +1187,13 @@
         </is>
       </c>
       <c r="G6" s="6" t="n">
-        <v>15452</v>
+        <v>19402</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>11058</v>
+        <v>16118</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>7908</v>
+        <v>10162</v>
       </c>
     </row>
     <row r="7">
@@ -1203,13 +1203,13 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>16592</v>
+        <v>18242</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>13622</v>
+        <v>19012</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>12938</v>
+        <v>17218</v>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
@@ -1217,13 +1217,13 @@
         </is>
       </c>
       <c r="G7" s="6" t="n">
-        <v>16242</v>
+        <v>19782</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>14992</v>
+        <v>17298</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>13182</v>
+        <v>16372</v>
       </c>
     </row>
     <row r="8">
@@ -1233,13 +1233,13 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>16262</v>
+        <v>21058</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>16338</v>
+        <v>17772</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>15492</v>
+        <v>19258</v>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
@@ -1247,13 +1247,13 @@
         </is>
       </c>
       <c r="G8" s="6" t="n">
-        <v>16062</v>
+        <v>21142</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>16402</v>
+        <v>19508</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>16022</v>
+        <v>17358</v>
       </c>
     </row>
     <row r="9">
@@ -1263,13 +1263,13 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>17472</v>
+        <v>18462</v>
       </c>
       <c r="C9" s="6" t="n">
-        <v>17428</v>
+        <v>20108</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>17572</v>
+        <v>22278</v>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
@@ -1277,13 +1277,13 @@
         </is>
       </c>
       <c r="G9" s="6" t="n">
-        <v>16352</v>
+        <v>19742</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>16918</v>
+        <v>19902</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>16792</v>
+        <v>23562</v>
       </c>
     </row>
     <row r="10">
@@ -1293,13 +1293,13 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>17728</v>
+        <v>21502</v>
       </c>
       <c r="C10" s="6" t="n">
-        <v>18698</v>
+        <v>22208</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>17712</v>
+        <v>23782</v>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
@@ -1307,13 +1307,13 @@
         </is>
       </c>
       <c r="G10" s="6" t="n">
-        <v>16478</v>
+        <v>18672</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>17292</v>
+        <v>20648</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>20452</v>
+        <v>22408</v>
       </c>
     </row>
     <row r="12">
@@ -1372,13 +1372,13 @@
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>18088</v>
+        <v>21048</v>
       </c>
       <c r="C14" s="6" t="n">
-        <v>15308</v>
+        <v>17822</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>12462</v>
+        <v>14838</v>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
@@ -1386,13 +1386,13 @@
         </is>
       </c>
       <c r="G14" s="6" t="n">
-        <v>18088</v>
+        <v>21048</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>15268</v>
+        <v>17922</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>13342</v>
+        <v>14172</v>
       </c>
     </row>
     <row r="15">
@@ -1402,13 +1402,13 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>18048</v>
+        <v>20478</v>
       </c>
       <c r="C15" s="6" t="n">
-        <v>15768</v>
+        <v>17452</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>12178</v>
+        <v>14972</v>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
@@ -1416,13 +1416,13 @@
         </is>
       </c>
       <c r="G15" s="6" t="n">
-        <v>18002</v>
+        <v>21078</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>16558</v>
+        <v>18948</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>13538</v>
+        <v>16858</v>
       </c>
     </row>
     <row r="16">
@@ -1432,13 +1432,13 @@
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>19062</v>
+        <v>23458</v>
       </c>
       <c r="C16" s="6" t="n">
-        <v>18892</v>
+        <v>21552</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>17148</v>
+        <v>21032</v>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
@@ -1446,13 +1446,13 @@
         </is>
       </c>
       <c r="G16" s="6" t="n">
-        <v>18458</v>
+        <v>20082</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>17538</v>
+        <v>21932</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>17258</v>
+        <v>22142</v>
       </c>
     </row>
     <row r="17">
@@ -1462,13 +1462,13 @@
         </is>
       </c>
       <c r="B17" s="6" t="n">
-        <v>18642</v>
+        <v>22332</v>
       </c>
       <c r="C17" s="6" t="n">
-        <v>18162</v>
+        <v>20562</v>
       </c>
       <c r="D17" s="6" t="n">
-        <v>18468</v>
+        <v>19678</v>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
@@ -1476,13 +1476,13 @@
         </is>
       </c>
       <c r="G17" s="6" t="n">
-        <v>17792</v>
+        <v>21242</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>18078</v>
+        <v>21972</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>18528</v>
+        <v>22052</v>
       </c>
     </row>
     <row r="18">
@@ -1492,13 +1492,13 @@
         </is>
       </c>
       <c r="B18" s="6" t="n">
-        <v>17322</v>
+        <v>22518</v>
       </c>
       <c r="C18" s="6" t="n">
-        <v>18742</v>
+        <v>22738</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>17582</v>
+        <v>22832</v>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
@@ -1506,13 +1506,13 @@
         </is>
       </c>
       <c r="G18" s="6" t="n">
-        <v>17388</v>
+        <v>21998</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>18572</v>
+        <v>21408</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>20718</v>
+        <v>21648</v>
       </c>
     </row>
     <row r="19">
@@ -1522,13 +1522,13 @@
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>19262</v>
+        <v>21998</v>
       </c>
       <c r="C19" s="6" t="n">
-        <v>21192</v>
+        <v>25792</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>21168</v>
+        <v>24142</v>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
@@ -1536,13 +1536,13 @@
         </is>
       </c>
       <c r="G19" s="6" t="n">
-        <v>18578</v>
+        <v>21482</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>20178</v>
+        <v>23492</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>21072</v>
+        <v>25498</v>
       </c>
     </row>
     <row r="21">
@@ -1601,13 +1601,13 @@
         </is>
       </c>
       <c r="B23" s="6" t="n">
-        <v>17408</v>
+        <v>21072</v>
       </c>
       <c r="C23" s="6" t="n">
-        <v>16668</v>
+        <v>19078</v>
       </c>
       <c r="D23" s="6" t="n">
-        <v>10468</v>
+        <v>13562</v>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
@@ -1615,13 +1615,13 @@
         </is>
       </c>
       <c r="G23" s="6" t="n">
-        <v>17408</v>
+        <v>21072</v>
       </c>
       <c r="H23" s="6" t="n">
-        <v>16148</v>
+        <v>17998</v>
       </c>
       <c r="I23" s="6" t="n">
-        <v>10092</v>
+        <v>13158</v>
       </c>
     </row>
     <row r="24">
@@ -1631,13 +1631,13 @@
         </is>
       </c>
       <c r="B24" s="6" t="n">
-        <v>18568</v>
+        <v>21722</v>
       </c>
       <c r="C24" s="6" t="n">
-        <v>16968</v>
+        <v>20752</v>
       </c>
       <c r="D24" s="6" t="n">
-        <v>4462</v>
+        <v>11362</v>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
@@ -1645,13 +1645,13 @@
         </is>
       </c>
       <c r="G24" s="6" t="n">
-        <v>18202</v>
+        <v>22808</v>
       </c>
       <c r="H24" s="6" t="n">
-        <v>18042</v>
+        <v>21298</v>
       </c>
       <c r="I24" s="6" t="n">
-        <v>8362</v>
+        <v>14228</v>
       </c>
     </row>
     <row r="25">
@@ -1661,13 +1661,13 @@
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>19438</v>
+        <v>24582</v>
       </c>
       <c r="C25" s="6" t="n">
-        <v>19588</v>
+        <v>24712</v>
       </c>
       <c r="D25" s="6" t="n">
-        <v>19592</v>
+        <v>26078</v>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
@@ -1675,13 +1675,13 @@
         </is>
       </c>
       <c r="G25" s="6" t="n">
-        <v>21002</v>
+        <v>24408</v>
       </c>
       <c r="H25" s="6" t="n">
-        <v>19918</v>
+        <v>25562</v>
       </c>
       <c r="I25" s="6" t="n">
-        <v>19922</v>
+        <v>25648</v>
       </c>
     </row>
     <row r="26">
@@ -1691,13 +1691,13 @@
         </is>
       </c>
       <c r="B26" s="6" t="n">
-        <v>20302</v>
+        <v>23842</v>
       </c>
       <c r="C26" s="6" t="n">
-        <v>20992</v>
+        <v>26892</v>
       </c>
       <c r="D26" s="6" t="n">
-        <v>24192</v>
+        <v>29398</v>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
@@ -1705,13 +1705,13 @@
         </is>
       </c>
       <c r="G26" s="6" t="n">
-        <v>20152</v>
+        <v>24218</v>
       </c>
       <c r="H26" s="6" t="n">
-        <v>22202</v>
+        <v>27108</v>
       </c>
       <c r="I26" s="6" t="n">
-        <v>23168</v>
+        <v>29812</v>
       </c>
     </row>
     <row r="27">
@@ -1721,13 +1721,13 @@
         </is>
       </c>
       <c r="B27" s="6" t="n">
-        <v>19188</v>
+        <v>23768</v>
       </c>
       <c r="C27" s="6" t="n">
-        <v>20588</v>
+        <v>26618</v>
       </c>
       <c r="D27" s="6" t="n">
-        <v>23472</v>
+        <v>29852</v>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
@@ -1735,13 +1735,13 @@
         </is>
       </c>
       <c r="G27" s="6" t="n">
-        <v>20158</v>
+        <v>23878</v>
       </c>
       <c r="H27" s="6" t="n">
-        <v>20778</v>
+        <v>26562</v>
       </c>
       <c r="I27" s="6" t="n">
-        <v>22832</v>
+        <v>30412</v>
       </c>
     </row>
     <row r="28">
@@ -1751,13 +1751,13 @@
         </is>
       </c>
       <c r="B28" s="6" t="n">
-        <v>19558</v>
+        <v>23122</v>
       </c>
       <c r="C28" s="6" t="n">
-        <v>21612</v>
+        <v>26572</v>
       </c>
       <c r="D28" s="6" t="n">
-        <v>23552</v>
+        <v>26472</v>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
@@ -1765,13 +1765,13 @@
         </is>
       </c>
       <c r="G28" s="6" t="n">
-        <v>20412</v>
+        <v>24412</v>
       </c>
       <c r="H28" s="6" t="n">
-        <v>22578</v>
+        <v>27128</v>
       </c>
       <c r="I28" s="6" t="n">
-        <v>21898</v>
+        <v>28648</v>
       </c>
     </row>
   </sheetData>
@@ -1941,13 +1941,13 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>19108</v>
+        <v>22412</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>18568</v>
+        <v>21212</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>18848</v>
+        <v>21178</v>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
@@ -1955,13 +1955,13 @@
         </is>
       </c>
       <c r="G5" s="6" t="n">
-        <v>19108</v>
+        <v>22412</v>
       </c>
       <c r="H5" s="6" t="n">
-        <v>18648</v>
+        <v>21248</v>
       </c>
       <c r="I5" s="6" t="n">
-        <v>18698</v>
+        <v>21138</v>
       </c>
     </row>
     <row r="6">
@@ -1971,13 +1971,13 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>20032</v>
+        <v>22392</v>
       </c>
       <c r="C6" s="6" t="n">
-        <v>19302</v>
+        <v>22388</v>
       </c>
       <c r="D6" s="6" t="n">
-        <v>18422</v>
+        <v>21892</v>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
@@ -1985,13 +1985,13 @@
         </is>
       </c>
       <c r="G6" s="6" t="n">
-        <v>18278</v>
+        <v>22502</v>
       </c>
       <c r="H6" s="6" t="n">
-        <v>18628</v>
+        <v>22032</v>
       </c>
       <c r="I6" s="6" t="n">
-        <v>18942</v>
+        <v>21642</v>
       </c>
     </row>
     <row r="7">
@@ -2001,13 +2001,13 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>18852</v>
+        <v>21638</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>18422</v>
+        <v>22332</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>18532</v>
+        <v>22082</v>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
@@ -2015,13 +2015,13 @@
         </is>
       </c>
       <c r="G7" s="6" t="n">
-        <v>18612</v>
+        <v>21982</v>
       </c>
       <c r="H7" s="6" t="n">
-        <v>18202</v>
+        <v>21958</v>
       </c>
       <c r="I7" s="6" t="n">
-        <v>19438</v>
+        <v>22908</v>
       </c>
     </row>
     <row r="8">
@@ -2031,13 +2031,13 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>18468</v>
+        <v>22212</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>18398</v>
+        <v>22132</v>
       </c>
       <c r="D8" s="6" t="n">
-        <v>18788</v>
+        <v>22392</v>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
@@ -2045,13 +2045,13 @@
         </is>
       </c>
       <c r="G8" s="6" t="n">
-        <v>18218</v>
+        <v>21722</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>18572</v>
+        <v>22258</v>
       </c>
       <c r="I8" s="6" t="n">
-        <v>18412</v>
+        <v>20682</v>
       </c>
     </row>
     <row r="9">
@@ -2061,13 +2061,13 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>18368</v>
+        <v>21458</v>
       </c>
       <c r="C9" s="6" t="n">
-        <v>17862</v>
+        <v>21148</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>18282</v>
+        <v>22872</v>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
@@ -2075,13 +2075,13 @@
         </is>
       </c>
       <c r="G9" s="6" t="n">
-        <v>17738</v>
+        <v>22388</v>
       </c>
       <c r="H9" s="6" t="n">
-        <v>17782</v>
+        <v>22118</v>
       </c>
       <c r="I9" s="6" t="n">
-        <v>18112</v>
+        <v>23162</v>
       </c>
     </row>
     <row r="10">
@@ -2091,13 +2091,13 @@
         </is>
       </c>
       <c r="B10" s="6" t="n">
-        <v>17842</v>
+        <v>21078</v>
       </c>
       <c r="C10" s="6" t="n">
-        <v>18788</v>
+        <v>21778</v>
       </c>
       <c r="D10" s="6" t="n">
-        <v>18582</v>
+        <v>22522</v>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
@@ -2105,13 +2105,13 @@
         </is>
       </c>
       <c r="G10" s="6" t="n">
-        <v>17572</v>
+        <v>20158</v>
       </c>
       <c r="H10" s="6" t="n">
-        <v>17868</v>
+        <v>21582</v>
       </c>
       <c r="I10" s="6" t="n">
-        <v>19528</v>
+        <v>21342</v>
       </c>
     </row>
     <row r="12">
@@ -2170,13 +2170,13 @@
         </is>
       </c>
       <c r="B14" s="6" t="n">
-        <v>19168</v>
+        <v>22272</v>
       </c>
       <c r="C14" s="6" t="n">
-        <v>19062</v>
+        <v>21462</v>
       </c>
       <c r="D14" s="6" t="n">
-        <v>18998</v>
+        <v>21332</v>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
@@ -2184,13 +2184,13 @@
         </is>
       </c>
       <c r="G14" s="6" t="n">
-        <v>19168</v>
+        <v>22272</v>
       </c>
       <c r="H14" s="6" t="n">
-        <v>19252</v>
+        <v>22252</v>
       </c>
       <c r="I14" s="6" t="n">
-        <v>19052</v>
+        <v>20888</v>
       </c>
     </row>
     <row r="15">
@@ -2200,13 +2200,13 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>19882</v>
+        <v>22502</v>
       </c>
       <c r="C15" s="6" t="n">
-        <v>20132</v>
+        <v>22932</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>18812</v>
+        <v>22072</v>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
@@ -2214,13 +2214,13 @@
         </is>
       </c>
       <c r="G15" s="6" t="n">
-        <v>19802</v>
+        <v>22592</v>
       </c>
       <c r="H15" s="6" t="n">
-        <v>20682</v>
+        <v>22732</v>
       </c>
       <c r="I15" s="6" t="n">
-        <v>20192</v>
+        <v>22812</v>
       </c>
     </row>
     <row r="16">
@@ -2230,13 +2230,13 @@
         </is>
       </c>
       <c r="B16" s="6" t="n">
-        <v>20338</v>
+        <v>23992</v>
       </c>
       <c r="C16" s="6" t="n">
-        <v>20102</v>
+        <v>22538</v>
       </c>
       <c r="D16" s="6" t="n">
-        <v>20438</v>
+        <v>24218</v>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
@@ -2244,13 +2244,13 @@
         </is>
       </c>
       <c r="G16" s="6" t="n">
-        <v>19382</v>
+        <v>21712</v>
       </c>
       <c r="H16" s="6" t="n">
-        <v>20168</v>
+        <v>23702</v>
       </c>
       <c r="I16" s="6" t="n">
-        <v>19982</v>
+        <v>24122</v>
       </c>
     </row>
     <row r="17">
@@ -2260,13 +2260,13 @@
         </is>
       </c>
       <c r="B17" s="6" t="n">
-        <v>19672</v>
+        <v>23332</v>
       </c>
       <c r="C17" s="6" t="n">
-        <v>19582</v>
+        <v>22868</v>
       </c>
       <c r="D17" s="6" t="n">
-        <v>19582</v>
+        <v>22358</v>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
@@ -2274,13 +2274,13 @@
         </is>
       </c>
       <c r="G17" s="6" t="n">
-        <v>18798</v>
+        <v>22812</v>
       </c>
       <c r="H17" s="6" t="n">
-        <v>19648</v>
+        <v>23522</v>
       </c>
       <c r="I17" s="6" t="n">
-        <v>19968</v>
+        <v>23528</v>
       </c>
     </row>
     <row r="18">
@@ -2290,13 +2290,13 @@
         </is>
       </c>
       <c r="B18" s="6" t="n">
-        <v>17578</v>
+        <v>23392</v>
       </c>
       <c r="C18" s="6" t="n">
-        <v>19438</v>
+        <v>22942</v>
       </c>
       <c r="D18" s="6" t="n">
-        <v>18968</v>
+        <v>22908</v>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
@@ -2304,13 +2304,13 @@
         </is>
       </c>
       <c r="G18" s="6" t="n">
-        <v>18798</v>
+        <v>22752</v>
       </c>
       <c r="H18" s="6" t="n">
-        <v>19392</v>
+        <v>22358</v>
       </c>
       <c r="I18" s="6" t="n">
-        <v>20268</v>
+        <v>23292</v>
       </c>
     </row>
     <row r="19">
@@ -2320,13 +2320,13 @@
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>18828</v>
+        <v>22918</v>
       </c>
       <c r="C19" s="6" t="n">
-        <v>20128</v>
+        <v>24498</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>19432</v>
+        <v>22758</v>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
@@ -2334,13 +2334,13 @@
         </is>
       </c>
       <c r="G19" s="6" t="n">
-        <v>18912</v>
+        <v>22728</v>
       </c>
       <c r="H19" s="6" t="n">
-        <v>18848</v>
+        <v>22662</v>
       </c>
       <c r="I19" s="6" t="n">
-        <v>19938</v>
+        <v>23872</v>
       </c>
     </row>
   </sheetData>

--- a/delay_pdf/11be/fix_nsta30_CwdsxQSRCxPSRC_sweep_onoff/param_p99_heatmap_1Mbps.xlsx
+++ b/delay_pdf/11be/fix_nsta30_CwdsxQSRCxPSRC_sweep_onoff/param_p99_heatmap_1Mbps.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="All STAs" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="P-EDCA STAs" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Legacy STAs" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="All STAs" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="P-EDCA STAs" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Legacy STAs" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -34,11 +34,11 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="0079C0FF"/>
+      <color rgb="00E3B341"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00E3B341"/>
+      <color rgb="0079C0FF"/>
     </font>
     <font>
       <b val="1"/>
@@ -98,7 +98,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -106,7 +106,10 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -484,7 +487,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -501,7 +504,7 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>All STAs — P99 VO delay heatmap (µs)   |   rows = QSRC, cols = PSRC   |   green = lower (better), red = higher</t>
+          <t>All STAs — delay heatmap (µs)   |   rows = QSRC, cols = PSRC   |   green = lower (better), red = higher</t>
         </is>
       </c>
     </row>
@@ -515,475 +518,2095 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">   P50</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
           <t>CWds=0</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>PSRC=1</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>PSRC=2</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>PSRC=3</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>CWds=1</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>PSRC=1</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>PSRC=2</t>
         </is>
       </c>
-      <c r="I4" s="4" t="inlineStr">
+      <c r="I5" s="5" t="inlineStr">
         <is>
           <t>PSRC=3</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>QSRC=0</t>
         </is>
       </c>
-      <c r="B5" s="6" t="n"/>
-      <c r="C5" s="6" t="n"/>
-      <c r="D5" s="6" t="n"/>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="B6" s="7" t="n">
+        <v>1698</v>
+      </c>
+      <c r="C6" s="7" t="n">
+        <v>1768</v>
+      </c>
+      <c r="D6" s="7" t="n">
+        <v>1738</v>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
         <is>
           <t>QSRC=0</t>
         </is>
       </c>
-      <c r="G5" s="6" t="n"/>
-      <c r="H5" s="6" t="n"/>
-      <c r="I5" s="6" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="G6" s="7" t="n">
+        <v>1698</v>
+      </c>
+      <c r="H6" s="7" t="n">
+        <v>1762</v>
+      </c>
+      <c r="I6" s="7" t="n">
+        <v>1782</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>QSRC=1</t>
         </is>
       </c>
-      <c r="B6" s="6" t="n"/>
-      <c r="C6" s="6" t="n"/>
-      <c r="D6" s="6" t="n"/>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="B7" s="7" t="n">
+        <v>1802</v>
+      </c>
+      <c r="C7" s="7" t="n">
+        <v>1848</v>
+      </c>
+      <c r="D7" s="7" t="n">
+        <v>1868</v>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
         <is>
           <t>QSRC=1</t>
         </is>
       </c>
-      <c r="G6" s="6" t="n"/>
-      <c r="H6" s="6" t="n"/>
-      <c r="I6" s="6" t="n"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="G7" s="7" t="n">
+        <v>1792</v>
+      </c>
+      <c r="H7" s="7" t="n">
+        <v>1842</v>
+      </c>
+      <c r="I7" s="7" t="n">
+        <v>1872</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>QSRC=2</t>
         </is>
       </c>
-      <c r="B7" s="6" t="n"/>
-      <c r="C7" s="6" t="n"/>
-      <c r="D7" s="6" t="n"/>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="B8" s="7" t="n">
+        <v>1752</v>
+      </c>
+      <c r="C8" s="7" t="n">
+        <v>1758</v>
+      </c>
+      <c r="D8" s="7" t="n">
+        <v>1762</v>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
         <is>
           <t>QSRC=2</t>
         </is>
       </c>
-      <c r="G7" s="6" t="n"/>
-      <c r="H7" s="6" t="n"/>
-      <c r="I7" s="6" t="n"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="G8" s="7" t="n">
+        <v>1748</v>
+      </c>
+      <c r="H8" s="7" t="n">
+        <v>1748</v>
+      </c>
+      <c r="I8" s="7" t="n">
+        <v>1742</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>QSRC=3</t>
         </is>
       </c>
-      <c r="B8" s="6" t="n"/>
-      <c r="C8" s="6" t="n"/>
-      <c r="D8" s="6" t="n"/>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="B9" s="7" t="n">
+        <v>1728</v>
+      </c>
+      <c r="C9" s="7" t="n">
+        <v>1688</v>
+      </c>
+      <c r="D9" s="7" t="n">
+        <v>1662</v>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
         <is>
           <t>QSRC=3</t>
         </is>
       </c>
-      <c r="G8" s="6" t="n"/>
-      <c r="H8" s="6" t="n"/>
-      <c r="I8" s="6" t="n"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="G9" s="7" t="n">
+        <v>1688</v>
+      </c>
+      <c r="H9" s="7" t="n">
+        <v>1708</v>
+      </c>
+      <c r="I9" s="7" t="n">
+        <v>1742</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>QSRC=4</t>
         </is>
       </c>
-      <c r="B9" s="6" t="n"/>
-      <c r="C9" s="6" t="n"/>
-      <c r="D9" s="6" t="n"/>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="B10" s="7" t="n">
+        <v>1758</v>
+      </c>
+      <c r="C10" s="7" t="n">
+        <v>1772</v>
+      </c>
+      <c r="D10" s="7" t="n">
+        <v>1758</v>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
         <is>
           <t>QSRC=4</t>
         </is>
       </c>
-      <c r="G9" s="6" t="n"/>
-      <c r="H9" s="6" t="n"/>
-      <c r="I9" s="6" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="G10" s="7" t="n">
+        <v>1752</v>
+      </c>
+      <c r="H10" s="7" t="n">
+        <v>1752</v>
+      </c>
+      <c r="I10" s="7" t="n">
+        <v>1772</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>QSRC=5</t>
         </is>
       </c>
-      <c r="B10" s="6" t="n"/>
-      <c r="C10" s="6" t="n"/>
-      <c r="D10" s="6" t="n"/>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="B11" s="7" t="n">
+        <v>1778</v>
+      </c>
+      <c r="C11" s="7" t="n">
+        <v>1782</v>
+      </c>
+      <c r="D11" s="7" t="n">
+        <v>1768</v>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
         <is>
           <t>QSRC=5</t>
         </is>
       </c>
-      <c r="G10" s="6" t="n"/>
-      <c r="H10" s="6" t="n"/>
-      <c r="I10" s="6" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>▼ nPedca = 15 / 30        (left block CWds=0   ·   right block CWds=1)</t>
-        </is>
+      <c r="G11" s="7" t="n">
+        <v>1772</v>
+      </c>
+      <c r="H11" s="7" t="n">
+        <v>1778</v>
+      </c>
+      <c r="I11" s="7" t="n">
+        <v>1762</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">   P95</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
           <t>CWds=0</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>PSRC=1</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>PSRC=2</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>PSRC=3</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="F14" s="4" t="inlineStr">
         <is>
           <t>CWds=1</t>
         </is>
       </c>
-      <c r="G13" s="4" t="inlineStr">
+      <c r="G14" s="5" t="inlineStr">
         <is>
           <t>PSRC=1</t>
         </is>
       </c>
-      <c r="H13" s="4" t="inlineStr">
+      <c r="H14" s="5" t="inlineStr">
         <is>
           <t>PSRC=2</t>
         </is>
       </c>
-      <c r="I13" s="4" t="inlineStr">
+      <c r="I14" s="5" t="inlineStr">
         <is>
           <t>PSRC=3</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>QSRC=0</t>
         </is>
       </c>
-      <c r="B14" s="6" t="n"/>
-      <c r="C14" s="6" t="n"/>
-      <c r="D14" s="6" t="n"/>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="B15" s="7" t="n">
+        <v>9802</v>
+      </c>
+      <c r="C15" s="7" t="n">
+        <v>10318</v>
+      </c>
+      <c r="D15" s="7" t="n">
+        <v>10032</v>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
         <is>
           <t>QSRC=0</t>
         </is>
       </c>
-      <c r="G14" s="6" t="n"/>
-      <c r="H14" s="6" t="n"/>
-      <c r="I14" s="6" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="G15" s="7" t="n">
+        <v>9802</v>
+      </c>
+      <c r="H15" s="7" t="n">
+        <v>10318</v>
+      </c>
+      <c r="I15" s="7" t="n">
+        <v>10302</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>QSRC=1</t>
         </is>
       </c>
-      <c r="B15" s="6" t="n"/>
-      <c r="C15" s="6" t="n"/>
-      <c r="D15" s="6" t="n"/>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="B16" s="7" t="n">
+        <v>9792</v>
+      </c>
+      <c r="C16" s="7" t="n">
+        <v>9882</v>
+      </c>
+      <c r="D16" s="7" t="n">
+        <v>10062</v>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
         <is>
           <t>QSRC=1</t>
         </is>
       </c>
-      <c r="G15" s="6" t="n"/>
-      <c r="H15" s="6" t="n"/>
-      <c r="I15" s="6" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="G16" s="7" t="n">
+        <v>9632</v>
+      </c>
+      <c r="H16" s="7" t="n">
+        <v>9812</v>
+      </c>
+      <c r="I16" s="7" t="n">
+        <v>9872</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>QSRC=2</t>
         </is>
       </c>
-      <c r="B16" s="6" t="n"/>
-      <c r="C16" s="6" t="n"/>
-      <c r="D16" s="6" t="n"/>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="B17" s="7" t="n">
+        <v>9628</v>
+      </c>
+      <c r="C17" s="7" t="n">
+        <v>9648</v>
+      </c>
+      <c r="D17" s="7" t="n">
+        <v>9598</v>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
         <is>
           <t>QSRC=2</t>
         </is>
       </c>
-      <c r="G16" s="6" t="n"/>
-      <c r="H16" s="6" t="n"/>
-      <c r="I16" s="6" t="n"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="G17" s="7" t="n">
+        <v>9468</v>
+      </c>
+      <c r="H17" s="7" t="n">
+        <v>9572</v>
+      </c>
+      <c r="I17" s="7" t="n">
+        <v>9582</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>QSRC=3</t>
         </is>
       </c>
-      <c r="B17" s="6" t="n"/>
-      <c r="C17" s="6" t="n"/>
-      <c r="D17" s="6" t="n"/>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="B18" s="7" t="n">
+        <v>9482</v>
+      </c>
+      <c r="C18" s="7" t="n">
+        <v>9338</v>
+      </c>
+      <c r="D18" s="7" t="n">
+        <v>9168</v>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
         <is>
           <t>QSRC=3</t>
         </is>
       </c>
-      <c r="G17" s="6" t="n"/>
-      <c r="H17" s="6" t="n"/>
-      <c r="I17" s="6" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="G18" s="7" t="n">
+        <v>9282</v>
+      </c>
+      <c r="H18" s="7" t="n">
+        <v>9408</v>
+      </c>
+      <c r="I18" s="7" t="n">
+        <v>9498</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>QSRC=4</t>
         </is>
       </c>
-      <c r="B18" s="6" t="n"/>
-      <c r="C18" s="6" t="n"/>
-      <c r="D18" s="6" t="n"/>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="B19" s="7" t="n">
+        <v>9338</v>
+      </c>
+      <c r="C19" s="7" t="n">
+        <v>9362</v>
+      </c>
+      <c r="D19" s="7" t="n">
+        <v>9318</v>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
         <is>
           <t>QSRC=4</t>
         </is>
       </c>
-      <c r="G18" s="6" t="n"/>
-      <c r="H18" s="6" t="n"/>
-      <c r="I18" s="6" t="n"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="G19" s="7" t="n">
+        <v>9348</v>
+      </c>
+      <c r="H19" s="7" t="n">
+        <v>9192</v>
+      </c>
+      <c r="I19" s="7" t="n">
+        <v>9322</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>QSRC=5</t>
         </is>
       </c>
-      <c r="B19" s="6" t="n"/>
-      <c r="C19" s="6" t="n"/>
-      <c r="D19" s="6" t="n"/>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="B20" s="7" t="n">
+        <v>9462</v>
+      </c>
+      <c r="C20" s="7" t="n">
+        <v>9442</v>
+      </c>
+      <c r="D20" s="7" t="n">
+        <v>9332</v>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
         <is>
           <t>QSRC=5</t>
         </is>
       </c>
-      <c r="G19" s="6" t="n"/>
-      <c r="H19" s="6" t="n"/>
-      <c r="I19" s="6" t="n"/>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>▼ nPedca = 30 / 30        (left block CWds=0   ·   right block CWds=1)</t>
-        </is>
+      <c r="G20" s="7" t="n">
+        <v>9462</v>
+      </c>
+      <c r="H20" s="7" t="n">
+        <v>9438</v>
+      </c>
+      <c r="I20" s="7" t="n">
+        <v>9362</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">   P99</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
           <t>CWds=0</t>
         </is>
       </c>
-      <c r="B22" s="4" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>PSRC=1</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr">
         <is>
           <t>PSRC=2</t>
         </is>
       </c>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>PSRC=3</t>
         </is>
       </c>
-      <c r="F22" s="3" t="inlineStr">
+      <c r="F23" s="4" t="inlineStr">
         <is>
           <t>CWds=1</t>
         </is>
       </c>
-      <c r="G22" s="4" t="inlineStr">
+      <c r="G23" s="5" t="inlineStr">
         <is>
           <t>PSRC=1</t>
         </is>
       </c>
-      <c r="H22" s="4" t="inlineStr">
+      <c r="H23" s="5" t="inlineStr">
         <is>
           <t>PSRC=2</t>
         </is>
       </c>
-      <c r="I22" s="4" t="inlineStr">
+      <c r="I23" s="5" t="inlineStr">
         <is>
           <t>PSRC=3</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>QSRC=0</t>
         </is>
       </c>
-      <c r="B23" s="6" t="n"/>
-      <c r="C23" s="6" t="n"/>
-      <c r="D23" s="6" t="n"/>
-      <c r="F23" s="5" t="inlineStr">
+      <c r="B24" s="7" t="n">
+        <v>14462</v>
+      </c>
+      <c r="C24" s="7" t="n">
+        <v>14922</v>
+      </c>
+      <c r="D24" s="7" t="n">
+        <v>14772</v>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
         <is>
           <t>QSRC=0</t>
         </is>
       </c>
-      <c r="G23" s="6" t="n"/>
-      <c r="H23" s="6" t="n"/>
-      <c r="I23" s="6" t="n"/>
-    </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
+      <c r="G24" s="7" t="n">
+        <v>14462</v>
+      </c>
+      <c r="H24" s="7" t="n">
+        <v>14958</v>
+      </c>
+      <c r="I24" s="7" t="n">
+        <v>15052</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t>QSRC=1</t>
         </is>
       </c>
-      <c r="B24" s="6" t="n"/>
-      <c r="C24" s="6" t="n"/>
-      <c r="D24" s="6" t="n"/>
-      <c r="F24" s="5" t="inlineStr">
+      <c r="B25" s="7" t="n">
+        <v>14172</v>
+      </c>
+      <c r="C25" s="7" t="n">
+        <v>14388</v>
+      </c>
+      <c r="D25" s="7" t="n">
+        <v>14618</v>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
         <is>
           <t>QSRC=1</t>
         </is>
       </c>
-      <c r="G24" s="6" t="n"/>
-      <c r="H24" s="6" t="n"/>
-      <c r="I24" s="6" t="n"/>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
+      <c r="G25" s="7" t="n">
+        <v>14148</v>
+      </c>
+      <c r="H25" s="7" t="n">
+        <v>14372</v>
+      </c>
+      <c r="I25" s="7" t="n">
+        <v>14618</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
         <is>
           <t>QSRC=2</t>
         </is>
       </c>
-      <c r="B25" s="6" t="n"/>
-      <c r="C25" s="6" t="n"/>
-      <c r="D25" s="6" t="n"/>
-      <c r="F25" s="5" t="inlineStr">
+      <c r="B26" s="7" t="n">
+        <v>14022</v>
+      </c>
+      <c r="C26" s="7" t="n">
+        <v>14218</v>
+      </c>
+      <c r="D26" s="7" t="n">
+        <v>14148</v>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
         <is>
           <t>QSRC=2</t>
         </is>
       </c>
-      <c r="G25" s="6" t="n"/>
-      <c r="H25" s="6" t="n"/>
-      <c r="I25" s="6" t="n"/>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
+      <c r="G26" s="7" t="n">
+        <v>13922</v>
+      </c>
+      <c r="H26" s="7" t="n">
+        <v>14232</v>
+      </c>
+      <c r="I26" s="7" t="n">
+        <v>14282</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
         <is>
           <t>QSRC=3</t>
         </is>
       </c>
-      <c r="B26" s="6" t="n"/>
-      <c r="C26" s="6" t="n"/>
-      <c r="D26" s="6" t="n"/>
-      <c r="F26" s="5" t="inlineStr">
+      <c r="B27" s="7" t="n">
+        <v>13938</v>
+      </c>
+      <c r="C27" s="7" t="n">
+        <v>13828</v>
+      </c>
+      <c r="D27" s="7" t="n">
+        <v>13722</v>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
         <is>
           <t>QSRC=3</t>
         </is>
       </c>
-      <c r="G26" s="6" t="n"/>
-      <c r="H26" s="6" t="n"/>
-      <c r="I26" s="6" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
+      <c r="G27" s="7" t="n">
+        <v>13668</v>
+      </c>
+      <c r="H27" s="7" t="n">
+        <v>13978</v>
+      </c>
+      <c r="I27" s="7" t="n">
+        <v>14088</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
         <is>
           <t>QSRC=4</t>
         </is>
       </c>
-      <c r="B27" s="6" t="n"/>
-      <c r="C27" s="6" t="n"/>
-      <c r="D27" s="6" t="n"/>
-      <c r="F27" s="5" t="inlineStr">
+      <c r="B28" s="7" t="n">
+        <v>13738</v>
+      </c>
+      <c r="C28" s="7" t="n">
+        <v>13842</v>
+      </c>
+      <c r="D28" s="7" t="n">
+        <v>13828</v>
+      </c>
+      <c r="F28" s="6" t="inlineStr">
         <is>
           <t>QSRC=4</t>
         </is>
       </c>
-      <c r="G27" s="6" t="n"/>
-      <c r="H27" s="6" t="n"/>
-      <c r="I27" s="6" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
+      <c r="G28" s="7" t="n">
+        <v>13718</v>
+      </c>
+      <c r="H28" s="7" t="n">
+        <v>13748</v>
+      </c>
+      <c r="I28" s="7" t="n">
+        <v>13838</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
         <is>
           <t>QSRC=5</t>
         </is>
       </c>
-      <c r="B28" s="6" t="n"/>
-      <c r="C28" s="6" t="n"/>
-      <c r="D28" s="6" t="n"/>
-      <c r="F28" s="5" t="inlineStr">
+      <c r="B29" s="7" t="n">
+        <v>13802</v>
+      </c>
+      <c r="C29" s="7" t="n">
+        <v>13792</v>
+      </c>
+      <c r="D29" s="7" t="n">
+        <v>13722</v>
+      </c>
+      <c r="F29" s="6" t="inlineStr">
         <is>
           <t>QSRC=5</t>
         </is>
       </c>
-      <c r="G28" s="6" t="n"/>
-      <c r="H28" s="6" t="n"/>
-      <c r="I28" s="6" t="n"/>
+      <c r="G29" s="7" t="n">
+        <v>13822</v>
+      </c>
+      <c r="H29" s="7" t="n">
+        <v>13752</v>
+      </c>
+      <c r="I29" s="7" t="n">
+        <v>13718</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>▼ nPedca = 15 / 30        (left block CWds=0   ·   right block CWds=1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   P50</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>CWds=0</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=1</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=2</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=3</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>CWds=1</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=1</t>
+        </is>
+      </c>
+      <c r="H34" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=2</t>
+        </is>
+      </c>
+      <c r="I34" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=0</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="n">
+        <v>1742</v>
+      </c>
+      <c r="C35" s="7" t="n">
+        <v>1778</v>
+      </c>
+      <c r="D35" s="7" t="n">
+        <v>1822</v>
+      </c>
+      <c r="F35" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=0</t>
+        </is>
+      </c>
+      <c r="G35" s="7" t="n">
+        <v>1742</v>
+      </c>
+      <c r="H35" s="7" t="n">
+        <v>1828</v>
+      </c>
+      <c r="I35" s="7" t="n">
+        <v>1932</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=1</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="n">
+        <v>1828</v>
+      </c>
+      <c r="C36" s="7" t="n">
+        <v>1932</v>
+      </c>
+      <c r="D36" s="7" t="n">
+        <v>1972</v>
+      </c>
+      <c r="F36" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=1</t>
+        </is>
+      </c>
+      <c r="G36" s="7" t="n">
+        <v>1898</v>
+      </c>
+      <c r="H36" s="7" t="n">
+        <v>2042</v>
+      </c>
+      <c r="I36" s="7" t="n">
+        <v>2092</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=2</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="n">
+        <v>1832</v>
+      </c>
+      <c r="C37" s="7" t="n">
+        <v>1798</v>
+      </c>
+      <c r="D37" s="7" t="n">
+        <v>1762</v>
+      </c>
+      <c r="F37" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=2</t>
+        </is>
+      </c>
+      <c r="G37" s="7" t="n">
+        <v>1762</v>
+      </c>
+      <c r="H37" s="7" t="n">
+        <v>1742</v>
+      </c>
+      <c r="I37" s="7" t="n">
+        <v>1748</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=3</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="n">
+        <v>1662</v>
+      </c>
+      <c r="C38" s="7" t="n">
+        <v>1698</v>
+      </c>
+      <c r="D38" s="7" t="n">
+        <v>1708</v>
+      </c>
+      <c r="F38" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=3</t>
+        </is>
+      </c>
+      <c r="G38" s="7" t="n">
+        <v>1658</v>
+      </c>
+      <c r="H38" s="7" t="n">
+        <v>1698</v>
+      </c>
+      <c r="I38" s="7" t="n">
+        <v>1738</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=4</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="n">
+        <v>1802</v>
+      </c>
+      <c r="C39" s="7" t="n">
+        <v>1838</v>
+      </c>
+      <c r="D39" s="7" t="n">
+        <v>1902</v>
+      </c>
+      <c r="F39" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=4</t>
+        </is>
+      </c>
+      <c r="G39" s="7" t="n">
+        <v>1808</v>
+      </c>
+      <c r="H39" s="7" t="n">
+        <v>1822</v>
+      </c>
+      <c r="I39" s="7" t="n">
+        <v>1858</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=5</t>
+        </is>
+      </c>
+      <c r="B40" s="7" t="n">
+        <v>1878</v>
+      </c>
+      <c r="C40" s="7" t="n">
+        <v>1892</v>
+      </c>
+      <c r="D40" s="7" t="n">
+        <v>1878</v>
+      </c>
+      <c r="F40" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=5</t>
+        </is>
+      </c>
+      <c r="G40" s="7" t="n">
+        <v>1858</v>
+      </c>
+      <c r="H40" s="7" t="n">
+        <v>1928</v>
+      </c>
+      <c r="I40" s="7" t="n">
+        <v>1938</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   P95</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>CWds=0</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=1</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=2</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=3</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>CWds=1</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=1</t>
+        </is>
+      </c>
+      <c r="H43" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=2</t>
+        </is>
+      </c>
+      <c r="I43" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=0</t>
+        </is>
+      </c>
+      <c r="B44" s="7" t="n">
+        <v>10542</v>
+      </c>
+      <c r="C44" s="7" t="n">
+        <v>10542</v>
+      </c>
+      <c r="D44" s="7" t="n">
+        <v>10822</v>
+      </c>
+      <c r="F44" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=0</t>
+        </is>
+      </c>
+      <c r="G44" s="7" t="n">
+        <v>10542</v>
+      </c>
+      <c r="H44" s="7" t="n">
+        <v>10798</v>
+      </c>
+      <c r="I44" s="7" t="n">
+        <v>11212</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=1</t>
+        </is>
+      </c>
+      <c r="B45" s="7" t="n">
+        <v>9702</v>
+      </c>
+      <c r="C45" s="7" t="n">
+        <v>10252</v>
+      </c>
+      <c r="D45" s="7" t="n">
+        <v>10408</v>
+      </c>
+      <c r="F45" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=1</t>
+        </is>
+      </c>
+      <c r="G45" s="7" t="n">
+        <v>10138</v>
+      </c>
+      <c r="H45" s="7" t="n">
+        <v>10632</v>
+      </c>
+      <c r="I45" s="7" t="n">
+        <v>10652</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=2</t>
+        </is>
+      </c>
+      <c r="B46" s="7" t="n">
+        <v>10048</v>
+      </c>
+      <c r="C46" s="7" t="n">
+        <v>10022</v>
+      </c>
+      <c r="D46" s="7" t="n">
+        <v>9832</v>
+      </c>
+      <c r="F46" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=2</t>
+        </is>
+      </c>
+      <c r="G46" s="7" t="n">
+        <v>9688</v>
+      </c>
+      <c r="H46" s="7" t="n">
+        <v>9772</v>
+      </c>
+      <c r="I46" s="7" t="n">
+        <v>10098</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=3</t>
+        </is>
+      </c>
+      <c r="B47" s="7" t="n">
+        <v>9298</v>
+      </c>
+      <c r="C47" s="7" t="n">
+        <v>9402</v>
+      </c>
+      <c r="D47" s="7" t="n">
+        <v>9512</v>
+      </c>
+      <c r="F47" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=3</t>
+        </is>
+      </c>
+      <c r="G47" s="7" t="n">
+        <v>9378</v>
+      </c>
+      <c r="H47" s="7" t="n">
+        <v>9282</v>
+      </c>
+      <c r="I47" s="7" t="n">
+        <v>9478</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=4</t>
+        </is>
+      </c>
+      <c r="B48" s="7" t="n">
+        <v>9212</v>
+      </c>
+      <c r="C48" s="7" t="n">
+        <v>9208</v>
+      </c>
+      <c r="D48" s="7" t="n">
+        <v>9502</v>
+      </c>
+      <c r="F48" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=4</t>
+        </is>
+      </c>
+      <c r="G48" s="7" t="n">
+        <v>9178</v>
+      </c>
+      <c r="H48" s="7" t="n">
+        <v>9138</v>
+      </c>
+      <c r="I48" s="7" t="n">
+        <v>9212</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=5</t>
+        </is>
+      </c>
+      <c r="B49" s="7" t="n">
+        <v>9588</v>
+      </c>
+      <c r="C49" s="7" t="n">
+        <v>9722</v>
+      </c>
+      <c r="D49" s="7" t="n">
+        <v>9588</v>
+      </c>
+      <c r="F49" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=5</t>
+        </is>
+      </c>
+      <c r="G49" s="7" t="n">
+        <v>9522</v>
+      </c>
+      <c r="H49" s="7" t="n">
+        <v>9812</v>
+      </c>
+      <c r="I49" s="7" t="n">
+        <v>9918</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   P99</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>CWds=0</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=1</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=2</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=3</t>
+        </is>
+      </c>
+      <c r="F52" s="4" t="inlineStr">
+        <is>
+          <t>CWds=1</t>
+        </is>
+      </c>
+      <c r="G52" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=1</t>
+        </is>
+      </c>
+      <c r="H52" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=2</t>
+        </is>
+      </c>
+      <c r="I52" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=0</t>
+        </is>
+      </c>
+      <c r="B53" s="7" t="n">
+        <v>15402</v>
+      </c>
+      <c r="C53" s="7" t="n">
+        <v>15632</v>
+      </c>
+      <c r="D53" s="7" t="n">
+        <v>15792</v>
+      </c>
+      <c r="F53" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=0</t>
+        </is>
+      </c>
+      <c r="G53" s="7" t="n">
+        <v>15402</v>
+      </c>
+      <c r="H53" s="7" t="n">
+        <v>15962</v>
+      </c>
+      <c r="I53" s="7" t="n">
+        <v>16458</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=1</t>
+        </is>
+      </c>
+      <c r="B54" s="7" t="n">
+        <v>14422</v>
+      </c>
+      <c r="C54" s="7" t="n">
+        <v>14982</v>
+      </c>
+      <c r="D54" s="7" t="n">
+        <v>15208</v>
+      </c>
+      <c r="F54" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=1</t>
+        </is>
+      </c>
+      <c r="G54" s="7" t="n">
+        <v>14798</v>
+      </c>
+      <c r="H54" s="7" t="n">
+        <v>15432</v>
+      </c>
+      <c r="I54" s="7" t="n">
+        <v>15712</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=2</t>
+        </is>
+      </c>
+      <c r="B55" s="7" t="n">
+        <v>14692</v>
+      </c>
+      <c r="C55" s="7" t="n">
+        <v>14962</v>
+      </c>
+      <c r="D55" s="7" t="n">
+        <v>14862</v>
+      </c>
+      <c r="F55" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=2</t>
+        </is>
+      </c>
+      <c r="G55" s="7" t="n">
+        <v>14462</v>
+      </c>
+      <c r="H55" s="7" t="n">
+        <v>14968</v>
+      </c>
+      <c r="I55" s="7" t="n">
+        <v>15338</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=3</t>
+        </is>
+      </c>
+      <c r="B56" s="7" t="n">
+        <v>14192</v>
+      </c>
+      <c r="C56" s="7" t="n">
+        <v>14482</v>
+      </c>
+      <c r="D56" s="7" t="n">
+        <v>14668</v>
+      </c>
+      <c r="F56" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=3</t>
+        </is>
+      </c>
+      <c r="G56" s="7" t="n">
+        <v>14212</v>
+      </c>
+      <c r="H56" s="7" t="n">
+        <v>14562</v>
+      </c>
+      <c r="I56" s="7" t="n">
+        <v>14782</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=4</t>
+        </is>
+      </c>
+      <c r="B57" s="7" t="n">
+        <v>14118</v>
+      </c>
+      <c r="C57" s="7" t="n">
+        <v>14172</v>
+      </c>
+      <c r="D57" s="7" t="n">
+        <v>14488</v>
+      </c>
+      <c r="F57" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=4</t>
+        </is>
+      </c>
+      <c r="G57" s="7" t="n">
+        <v>13992</v>
+      </c>
+      <c r="H57" s="7" t="n">
+        <v>14122</v>
+      </c>
+      <c r="I57" s="7" t="n">
+        <v>14372</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=5</t>
+        </is>
+      </c>
+      <c r="B58" s="7" t="n">
+        <v>14138</v>
+      </c>
+      <c r="C58" s="7" t="n">
+        <v>14202</v>
+      </c>
+      <c r="D58" s="7" t="n">
+        <v>14088</v>
+      </c>
+      <c r="F58" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=5</t>
+        </is>
+      </c>
+      <c r="G58" s="7" t="n">
+        <v>14022</v>
+      </c>
+      <c r="H58" s="7" t="n">
+        <v>14348</v>
+      </c>
+      <c r="I58" s="7" t="n">
+        <v>14482</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>▼ nPedca = 30 / 30        (left block CWds=0   ·   right block CWds=1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   P50</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>CWds=0</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=1</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=2</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=3</t>
+        </is>
+      </c>
+      <c r="F63" s="4" t="inlineStr">
+        <is>
+          <t>CWds=1</t>
+        </is>
+      </c>
+      <c r="G63" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=1</t>
+        </is>
+      </c>
+      <c r="H63" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=2</t>
+        </is>
+      </c>
+      <c r="I63" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=0</t>
+        </is>
+      </c>
+      <c r="B64" s="7" t="n">
+        <v>1798</v>
+      </c>
+      <c r="C64" s="7" t="n">
+        <v>1838</v>
+      </c>
+      <c r="D64" s="7" t="n">
+        <v>1862</v>
+      </c>
+      <c r="F64" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=0</t>
+        </is>
+      </c>
+      <c r="G64" s="7" t="n">
+        <v>1798</v>
+      </c>
+      <c r="H64" s="7" t="n">
+        <v>1868</v>
+      </c>
+      <c r="I64" s="7" t="n">
+        <v>1962</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=1</t>
+        </is>
+      </c>
+      <c r="B65" s="7" t="n">
+        <v>1922</v>
+      </c>
+      <c r="C65" s="7" t="n">
+        <v>1948</v>
+      </c>
+      <c r="D65" s="7" t="n">
+        <v>2028</v>
+      </c>
+      <c r="F65" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=1</t>
+        </is>
+      </c>
+      <c r="G65" s="7" t="n">
+        <v>1972</v>
+      </c>
+      <c r="H65" s="7" t="n">
+        <v>2092</v>
+      </c>
+      <c r="I65" s="7" t="n">
+        <v>2208</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=2</t>
+        </is>
+      </c>
+      <c r="B66" s="7" t="n">
+        <v>1798</v>
+      </c>
+      <c r="C66" s="7" t="n">
+        <v>1792</v>
+      </c>
+      <c r="D66" s="7" t="n">
+        <v>1778</v>
+      </c>
+      <c r="F66" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=2</t>
+        </is>
+      </c>
+      <c r="G66" s="7" t="n">
+        <v>1802</v>
+      </c>
+      <c r="H66" s="7" t="n">
+        <v>1752</v>
+      </c>
+      <c r="I66" s="7" t="n">
+        <v>1718</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=3</t>
+        </is>
+      </c>
+      <c r="B67" s="7" t="n">
+        <v>1642</v>
+      </c>
+      <c r="C67" s="7" t="n">
+        <v>1698</v>
+      </c>
+      <c r="D67" s="7" t="n">
+        <v>1758</v>
+      </c>
+      <c r="F67" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=3</t>
+        </is>
+      </c>
+      <c r="G67" s="7" t="n">
+        <v>1648</v>
+      </c>
+      <c r="H67" s="7" t="n">
+        <v>1672</v>
+      </c>
+      <c r="I67" s="7" t="n">
+        <v>1762</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=4</t>
+        </is>
+      </c>
+      <c r="B68" s="7" t="n">
+        <v>1862</v>
+      </c>
+      <c r="C68" s="7" t="n">
+        <v>1898</v>
+      </c>
+      <c r="D68" s="7" t="n">
+        <v>1942</v>
+      </c>
+      <c r="F68" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=4</t>
+        </is>
+      </c>
+      <c r="G68" s="7" t="n">
+        <v>1898</v>
+      </c>
+      <c r="H68" s="7" t="n">
+        <v>1978</v>
+      </c>
+      <c r="I68" s="7" t="n">
+        <v>2028</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=5</t>
+        </is>
+      </c>
+      <c r="B69" s="7" t="n">
+        <v>1938</v>
+      </c>
+      <c r="C69" s="7" t="n">
+        <v>2018</v>
+      </c>
+      <c r="D69" s="7" t="n">
+        <v>1982</v>
+      </c>
+      <c r="F69" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=5</t>
+        </is>
+      </c>
+      <c r="G69" s="7" t="n">
+        <v>1892</v>
+      </c>
+      <c r="H69" s="7" t="n">
+        <v>2038</v>
+      </c>
+      <c r="I69" s="7" t="n">
+        <v>2128</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   P95</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>CWds=0</t>
+        </is>
+      </c>
+      <c r="B72" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=1</t>
+        </is>
+      </c>
+      <c r="C72" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=2</t>
+        </is>
+      </c>
+      <c r="D72" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=3</t>
+        </is>
+      </c>
+      <c r="F72" s="4" t="inlineStr">
+        <is>
+          <t>CWds=1</t>
+        </is>
+      </c>
+      <c r="G72" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=1</t>
+        </is>
+      </c>
+      <c r="H72" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=2</t>
+        </is>
+      </c>
+      <c r="I72" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=0</t>
+        </is>
+      </c>
+      <c r="B73" s="7" t="n">
+        <v>10862</v>
+      </c>
+      <c r="C73" s="7" t="n">
+        <v>10922</v>
+      </c>
+      <c r="D73" s="7" t="n">
+        <v>10692</v>
+      </c>
+      <c r="F73" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=0</t>
+        </is>
+      </c>
+      <c r="G73" s="7" t="n">
+        <v>10862</v>
+      </c>
+      <c r="H73" s="7" t="n">
+        <v>10722</v>
+      </c>
+      <c r="I73" s="7" t="n">
+        <v>10912</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=1</t>
+        </is>
+      </c>
+      <c r="B74" s="7" t="n">
+        <v>10298</v>
+      </c>
+      <c r="C74" s="7" t="n">
+        <v>10148</v>
+      </c>
+      <c r="D74" s="7" t="n">
+        <v>10668</v>
+      </c>
+      <c r="F74" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=1</t>
+        </is>
+      </c>
+      <c r="G74" s="7" t="n">
+        <v>10388</v>
+      </c>
+      <c r="H74" s="7" t="n">
+        <v>10622</v>
+      </c>
+      <c r="I74" s="7" t="n">
+        <v>10852</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=2</t>
+        </is>
+      </c>
+      <c r="B75" s="7" t="n">
+        <v>9958</v>
+      </c>
+      <c r="C75" s="7" t="n">
+        <v>10072</v>
+      </c>
+      <c r="D75" s="7" t="n">
+        <v>10032</v>
+      </c>
+      <c r="F75" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=2</t>
+        </is>
+      </c>
+      <c r="G75" s="7" t="n">
+        <v>10052</v>
+      </c>
+      <c r="H75" s="7" t="n">
+        <v>10042</v>
+      </c>
+      <c r="I75" s="7" t="n">
+        <v>10248</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=3</t>
+        </is>
+      </c>
+      <c r="B76" s="7" t="n">
+        <v>9132</v>
+      </c>
+      <c r="C76" s="7" t="n">
+        <v>9522</v>
+      </c>
+      <c r="D76" s="7" t="n">
+        <v>9908</v>
+      </c>
+      <c r="F76" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=3</t>
+        </is>
+      </c>
+      <c r="G76" s="7" t="n">
+        <v>9238</v>
+      </c>
+      <c r="H76" s="7" t="n">
+        <v>8952</v>
+      </c>
+      <c r="I76" s="7" t="n">
+        <v>9202</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=4</t>
+        </is>
+      </c>
+      <c r="B77" s="7" t="n">
+        <v>8948</v>
+      </c>
+      <c r="C77" s="7" t="n">
+        <v>9078</v>
+      </c>
+      <c r="D77" s="7" t="n">
+        <v>9232</v>
+      </c>
+      <c r="F77" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=4</t>
+        </is>
+      </c>
+      <c r="G77" s="7" t="n">
+        <v>9152</v>
+      </c>
+      <c r="H77" s="7" t="n">
+        <v>9248</v>
+      </c>
+      <c r="I77" s="7" t="n">
+        <v>9422</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=5</t>
+        </is>
+      </c>
+      <c r="B78" s="7" t="n">
+        <v>9652</v>
+      </c>
+      <c r="C78" s="7" t="n">
+        <v>9942</v>
+      </c>
+      <c r="D78" s="7" t="n">
+        <v>10058</v>
+      </c>
+      <c r="F78" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=5</t>
+        </is>
+      </c>
+      <c r="G78" s="7" t="n">
+        <v>9472</v>
+      </c>
+      <c r="H78" s="7" t="n">
+        <v>10212</v>
+      </c>
+      <c r="I78" s="7" t="n">
+        <v>10718</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   P99</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="4" t="inlineStr">
+        <is>
+          <t>CWds=0</t>
+        </is>
+      </c>
+      <c r="B81" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=1</t>
+        </is>
+      </c>
+      <c r="C81" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=2</t>
+        </is>
+      </c>
+      <c r="D81" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=3</t>
+        </is>
+      </c>
+      <c r="F81" s="4" t="inlineStr">
+        <is>
+          <t>CWds=1</t>
+        </is>
+      </c>
+      <c r="G81" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=1</t>
+        </is>
+      </c>
+      <c r="H81" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=2</t>
+        </is>
+      </c>
+      <c r="I81" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=0</t>
+        </is>
+      </c>
+      <c r="B82" s="7" t="n">
+        <v>15972</v>
+      </c>
+      <c r="C82" s="7" t="n">
+        <v>16082</v>
+      </c>
+      <c r="D82" s="7" t="n">
+        <v>15928</v>
+      </c>
+      <c r="F82" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=0</t>
+        </is>
+      </c>
+      <c r="G82" s="7" t="n">
+        <v>15972</v>
+      </c>
+      <c r="H82" s="7" t="n">
+        <v>16068</v>
+      </c>
+      <c r="I82" s="7" t="n">
+        <v>16358</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=1</t>
+        </is>
+      </c>
+      <c r="B83" s="7" t="n">
+        <v>15032</v>
+      </c>
+      <c r="C83" s="7" t="n">
+        <v>15092</v>
+      </c>
+      <c r="D83" s="7" t="n">
+        <v>15668</v>
+      </c>
+      <c r="F83" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=1</t>
+        </is>
+      </c>
+      <c r="G83" s="7" t="n">
+        <v>15068</v>
+      </c>
+      <c r="H83" s="7" t="n">
+        <v>15688</v>
+      </c>
+      <c r="I83" s="7" t="n">
+        <v>16078</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=2</t>
+        </is>
+      </c>
+      <c r="B84" s="7" t="n">
+        <v>15052</v>
+      </c>
+      <c r="C84" s="7" t="n">
+        <v>15402</v>
+      </c>
+      <c r="D84" s="7" t="n">
+        <v>15312</v>
+      </c>
+      <c r="F84" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=2</t>
+        </is>
+      </c>
+      <c r="G84" s="7" t="n">
+        <v>15078</v>
+      </c>
+      <c r="H84" s="7" t="n">
+        <v>15612</v>
+      </c>
+      <c r="I84" s="7" t="n">
+        <v>16102</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=3</t>
+        </is>
+      </c>
+      <c r="B85" s="7" t="n">
+        <v>14472</v>
+      </c>
+      <c r="C85" s="7" t="n">
+        <v>15058</v>
+      </c>
+      <c r="D85" s="7" t="n">
+        <v>15492</v>
+      </c>
+      <c r="F85" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=3</t>
+        </is>
+      </c>
+      <c r="G85" s="7" t="n">
+        <v>14612</v>
+      </c>
+      <c r="H85" s="7" t="n">
+        <v>14992</v>
+      </c>
+      <c r="I85" s="7" t="n">
+        <v>15528</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=4</t>
+        </is>
+      </c>
+      <c r="B86" s="7" t="n">
+        <v>14248</v>
+      </c>
+      <c r="C86" s="7" t="n">
+        <v>14462</v>
+      </c>
+      <c r="D86" s="7" t="n">
+        <v>14648</v>
+      </c>
+      <c r="F86" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=4</t>
+        </is>
+      </c>
+      <c r="G86" s="7" t="n">
+        <v>14328</v>
+      </c>
+      <c r="H86" s="7" t="n">
+        <v>14708</v>
+      </c>
+      <c r="I86" s="7" t="n">
+        <v>15002</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=5</t>
+        </is>
+      </c>
+      <c r="B87" s="7" t="n">
+        <v>14162</v>
+      </c>
+      <c r="C87" s="7" t="n">
+        <v>14548</v>
+      </c>
+      <c r="D87" s="7" t="n">
+        <v>14638</v>
+      </c>
+      <c r="F87" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=5</t>
+        </is>
+      </c>
+      <c r="G87" s="7" t="n">
+        <v>14062</v>
+      </c>
+      <c r="H87" s="7" t="n">
+        <v>14792</v>
+      </c>
+      <c r="I87" s="7" t="n">
+        <v>15348</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="13">
+    <mergeCell ref="A33:I33"/>
+    <mergeCell ref="A51:I51"/>
+    <mergeCell ref="A71:I71"/>
+    <mergeCell ref="A42:I42"/>
+    <mergeCell ref="A32:I32"/>
+    <mergeCell ref="A13:I13"/>
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A12:I12"/>
-    <mergeCell ref="A21:I21"/>
+    <mergeCell ref="A80:I80"/>
     <mergeCell ref="A3:I3"/>
+    <mergeCell ref="A61:I61"/>
+    <mergeCell ref="A22:I22"/>
+    <mergeCell ref="A4:I4"/>
+    <mergeCell ref="A62:I62"/>
   </mergeCells>
-  <conditionalFormatting sqref="B5:D10">
+  <conditionalFormatting sqref="B6:D11">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -995,7 +2618,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G5:I10">
+  <conditionalFormatting sqref="G6:I11">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -1007,7 +2630,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B14:D19">
+  <conditionalFormatting sqref="B15:D20">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -1019,7 +2642,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G14:I19">
+  <conditionalFormatting sqref="G15:I20">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -1031,7 +2654,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B23:D28">
+  <conditionalFormatting sqref="B24:D29">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
@@ -1043,8 +2666,152 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G23:I28">
+  <conditionalFormatting sqref="G24:I29">
     <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="002DA44E"/>
+        <color rgb="00E3B341"/>
+        <color rgb="00F85149"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B35:D40">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="002DA44E"/>
+        <color rgb="00E3B341"/>
+        <color rgb="00F85149"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G35:I40">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="002DA44E"/>
+        <color rgb="00E3B341"/>
+        <color rgb="00F85149"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B44:D49">
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="002DA44E"/>
+        <color rgb="00E3B341"/>
+        <color rgb="00F85149"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G44:I49">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="002DA44E"/>
+        <color rgb="00E3B341"/>
+        <color rgb="00F85149"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B53:D58">
+    <cfRule type="colorScale" priority="11">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="002DA44E"/>
+        <color rgb="00E3B341"/>
+        <color rgb="00F85149"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G53:I58">
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="002DA44E"/>
+        <color rgb="00E3B341"/>
+        <color rgb="00F85149"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B64:D69">
+    <cfRule type="colorScale" priority="13">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="002DA44E"/>
+        <color rgb="00E3B341"/>
+        <color rgb="00F85149"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G64:I69">
+    <cfRule type="colorScale" priority="14">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="002DA44E"/>
+        <color rgb="00E3B341"/>
+        <color rgb="00F85149"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B73:D78">
+    <cfRule type="colorScale" priority="15">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="002DA44E"/>
+        <color rgb="00E3B341"/>
+        <color rgb="00F85149"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G73:I78">
+    <cfRule type="colorScale" priority="16">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="002DA44E"/>
+        <color rgb="00E3B341"/>
+        <color rgb="00F85149"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B82:D87">
+    <cfRule type="colorScale" priority="17">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="002DA44E"/>
+        <color rgb="00E3B341"/>
+        <color rgb="00F85149"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G82:I87">
+    <cfRule type="colorScale" priority="18">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -1066,7 +2833,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I28"/>
+  <dimension ref="A1:I87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1083,7 +2850,7 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>P-EDCA STAs — P99 VO delay heatmap (µs)   |   rows = QSRC, cols = PSRC   |   green = lower (better), red = higher</t>
+          <t>P-EDCA STAs — delay heatmap (µs)   |   rows = QSRC, cols = PSRC   |   green = lower (better), red = higher</t>
         </is>
       </c>
     </row>
@@ -1097,691 +2864,2095 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">   P50</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
           <t>CWds=0</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>PSRC=1</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>PSRC=2</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>PSRC=3</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>CWds=1</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>PSRC=1</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>PSRC=2</t>
         </is>
       </c>
-      <c r="I4" s="4" t="inlineStr">
+      <c r="I5" s="5" t="inlineStr">
         <is>
           <t>PSRC=3</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>QSRC=0</t>
         </is>
       </c>
-      <c r="B5" s="6" t="n">
-        <v>21858</v>
-      </c>
-      <c r="C5" s="6" t="n">
-        <v>15702</v>
-      </c>
-      <c r="D5" s="6" t="n">
-        <v>9428</v>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="B6" s="7" t="n">
+        <v>1422</v>
+      </c>
+      <c r="C6" s="7" t="n">
+        <v>1472</v>
+      </c>
+      <c r="D6" s="7" t="n">
+        <v>1482</v>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
         <is>
           <t>QSRC=0</t>
         </is>
       </c>
-      <c r="G5" s="6" t="n">
-        <v>21858</v>
-      </c>
-      <c r="H5" s="6" t="n">
-        <v>16678</v>
-      </c>
-      <c r="I5" s="6" t="n">
-        <v>9312</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="G6" s="7" t="n">
+        <v>1422</v>
+      </c>
+      <c r="H6" s="7" t="n">
+        <v>1482</v>
+      </c>
+      <c r="I6" s="7" t="n">
+        <v>1532</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>QSRC=1</t>
         </is>
       </c>
-      <c r="B6" s="6" t="n">
-        <v>19668</v>
-      </c>
-      <c r="C6" s="6" t="n">
-        <v>14322</v>
-      </c>
-      <c r="D6" s="6" t="n">
-        <v>10482</v>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="B7" s="7" t="n">
+        <v>1712</v>
+      </c>
+      <c r="C7" s="7" t="n">
+        <v>1762</v>
+      </c>
+      <c r="D7" s="7" t="n">
+        <v>1782</v>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
         <is>
           <t>QSRC=1</t>
         </is>
       </c>
-      <c r="G6" s="6" t="n">
-        <v>19402</v>
-      </c>
-      <c r="H6" s="6" t="n">
-        <v>16118</v>
-      </c>
-      <c r="I6" s="6" t="n">
-        <v>10162</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="G7" s="7" t="n">
+        <v>1738</v>
+      </c>
+      <c r="H7" s="7" t="n">
+        <v>1782</v>
+      </c>
+      <c r="I7" s="7" t="n">
+        <v>1818</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>QSRC=2</t>
         </is>
       </c>
-      <c r="B7" s="6" t="n">
-        <v>18242</v>
-      </c>
-      <c r="C7" s="6" t="n">
-        <v>19012</v>
-      </c>
-      <c r="D7" s="6" t="n">
-        <v>17218</v>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="B8" s="7" t="n">
+        <v>1542</v>
+      </c>
+      <c r="C8" s="7" t="n">
+        <v>1478</v>
+      </c>
+      <c r="D8" s="7" t="n">
+        <v>1458</v>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
         <is>
           <t>QSRC=2</t>
         </is>
       </c>
-      <c r="G7" s="6" t="n">
-        <v>19782</v>
-      </c>
-      <c r="H7" s="6" t="n">
-        <v>17298</v>
-      </c>
-      <c r="I7" s="6" t="n">
-        <v>16372</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="G8" s="7" t="n">
+        <v>1542</v>
+      </c>
+      <c r="H8" s="7" t="n">
+        <v>1432</v>
+      </c>
+      <c r="I8" s="7" t="n">
+        <v>1388</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>QSRC=3</t>
         </is>
       </c>
-      <c r="B8" s="6" t="n">
-        <v>21058</v>
-      </c>
-      <c r="C8" s="6" t="n">
-        <v>17772</v>
-      </c>
-      <c r="D8" s="6" t="n">
-        <v>19258</v>
-      </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="B9" s="7" t="n">
+        <v>1432</v>
+      </c>
+      <c r="C9" s="7" t="n">
+        <v>1408</v>
+      </c>
+      <c r="D9" s="7" t="n">
+        <v>1368</v>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
         <is>
           <t>QSRC=3</t>
         </is>
       </c>
-      <c r="G8" s="6" t="n">
-        <v>21142</v>
-      </c>
-      <c r="H8" s="6" t="n">
-        <v>19508</v>
-      </c>
-      <c r="I8" s="6" t="n">
-        <v>17358</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="G9" s="7" t="n">
+        <v>1428</v>
+      </c>
+      <c r="H9" s="7" t="n">
+        <v>1402</v>
+      </c>
+      <c r="I9" s="7" t="n">
+        <v>1428</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>QSRC=4</t>
         </is>
       </c>
-      <c r="B9" s="6" t="n">
-        <v>18462</v>
-      </c>
-      <c r="C9" s="6" t="n">
-        <v>20108</v>
-      </c>
-      <c r="D9" s="6" t="n">
-        <v>22278</v>
-      </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="B10" s="7" t="n">
+        <v>1688</v>
+      </c>
+      <c r="C10" s="7" t="n">
+        <v>1698</v>
+      </c>
+      <c r="D10" s="7" t="n">
+        <v>1662</v>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
         <is>
           <t>QSRC=4</t>
         </is>
       </c>
-      <c r="G9" s="6" t="n">
-        <v>19742</v>
-      </c>
-      <c r="H9" s="6" t="n">
-        <v>19902</v>
-      </c>
-      <c r="I9" s="6" t="n">
-        <v>23562</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="G10" s="7" t="n">
+        <v>1692</v>
+      </c>
+      <c r="H10" s="7" t="n">
+        <v>1668</v>
+      </c>
+      <c r="I10" s="7" t="n">
+        <v>1712</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>QSRC=5</t>
         </is>
       </c>
-      <c r="B10" s="6" t="n">
-        <v>21502</v>
-      </c>
-      <c r="C10" s="6" t="n">
-        <v>22208</v>
-      </c>
-      <c r="D10" s="6" t="n">
-        <v>23782</v>
-      </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="B11" s="7" t="n">
+        <v>1778</v>
+      </c>
+      <c r="C11" s="7" t="n">
+        <v>1828</v>
+      </c>
+      <c r="D11" s="7" t="n">
+        <v>1822</v>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
         <is>
           <t>QSRC=5</t>
         </is>
       </c>
-      <c r="G10" s="6" t="n">
-        <v>18672</v>
-      </c>
-      <c r="H10" s="6" t="n">
-        <v>20648</v>
-      </c>
-      <c r="I10" s="6" t="n">
-        <v>22408</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>▼ nPedca = 15 / 30        (left block CWds=0   ·   right block CWds=1)</t>
-        </is>
+      <c r="G11" s="7" t="n">
+        <v>1802</v>
+      </c>
+      <c r="H11" s="7" t="n">
+        <v>1798</v>
+      </c>
+      <c r="I11" s="7" t="n">
+        <v>1792</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">   P95</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
           <t>CWds=0</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>PSRC=1</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>PSRC=2</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>PSRC=3</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="F14" s="4" t="inlineStr">
         <is>
           <t>CWds=1</t>
         </is>
       </c>
-      <c r="G13" s="4" t="inlineStr">
+      <c r="G14" s="5" t="inlineStr">
         <is>
           <t>PSRC=1</t>
         </is>
       </c>
-      <c r="H13" s="4" t="inlineStr">
+      <c r="H14" s="5" t="inlineStr">
         <is>
           <t>PSRC=2</t>
         </is>
       </c>
-      <c r="I13" s="4" t="inlineStr">
+      <c r="I14" s="5" t="inlineStr">
         <is>
           <t>PSRC=3</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>QSRC=0</t>
         </is>
       </c>
-      <c r="B14" s="6" t="n">
-        <v>21048</v>
-      </c>
-      <c r="C14" s="6" t="n">
-        <v>17822</v>
-      </c>
-      <c r="D14" s="6" t="n">
-        <v>14838</v>
-      </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="B15" s="7" t="n">
+        <v>6978</v>
+      </c>
+      <c r="C15" s="7" t="n">
+        <v>5382</v>
+      </c>
+      <c r="D15" s="7" t="n">
+        <v>4788</v>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
         <is>
           <t>QSRC=0</t>
         </is>
       </c>
-      <c r="G14" s="6" t="n">
-        <v>21048</v>
-      </c>
-      <c r="H14" s="6" t="n">
-        <v>17922</v>
-      </c>
-      <c r="I14" s="6" t="n">
-        <v>14172</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="G15" s="7" t="n">
+        <v>6978</v>
+      </c>
+      <c r="H15" s="7" t="n">
+        <v>4442</v>
+      </c>
+      <c r="I15" s="7" t="n">
+        <v>4062</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>QSRC=1</t>
         </is>
       </c>
-      <c r="B15" s="6" t="n">
-        <v>20478</v>
-      </c>
-      <c r="C15" s="6" t="n">
-        <v>17452</v>
-      </c>
-      <c r="D15" s="6" t="n">
-        <v>14972</v>
-      </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="B16" s="7" t="n">
+        <v>6528</v>
+      </c>
+      <c r="C16" s="7" t="n">
+        <v>4778</v>
+      </c>
+      <c r="D16" s="7" t="n">
+        <v>4822</v>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
         <is>
           <t>QSRC=1</t>
         </is>
       </c>
-      <c r="G15" s="6" t="n">
-        <v>21078</v>
-      </c>
-      <c r="H15" s="6" t="n">
-        <v>18948</v>
-      </c>
-      <c r="I15" s="6" t="n">
-        <v>16858</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="G16" s="7" t="n">
+        <v>6768</v>
+      </c>
+      <c r="H16" s="7" t="n">
+        <v>4632</v>
+      </c>
+      <c r="I16" s="7" t="n">
+        <v>4232</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>QSRC=2</t>
         </is>
       </c>
-      <c r="B16" s="6" t="n">
-        <v>23458</v>
-      </c>
-      <c r="C16" s="6" t="n">
-        <v>21552</v>
-      </c>
-      <c r="D16" s="6" t="n">
-        <v>21032</v>
-      </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="B17" s="7" t="n">
+        <v>6428</v>
+      </c>
+      <c r="C17" s="7" t="n">
+        <v>4722</v>
+      </c>
+      <c r="D17" s="7" t="n">
+        <v>4472</v>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
         <is>
           <t>QSRC=2</t>
         </is>
       </c>
-      <c r="G16" s="6" t="n">
-        <v>20082</v>
-      </c>
-      <c r="H16" s="6" t="n">
-        <v>21932</v>
-      </c>
-      <c r="I16" s="6" t="n">
-        <v>22142</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="G17" s="7" t="n">
+        <v>6148</v>
+      </c>
+      <c r="H17" s="7" t="n">
+        <v>4352</v>
+      </c>
+      <c r="I17" s="7" t="n">
+        <v>4262</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>QSRC=3</t>
         </is>
       </c>
-      <c r="B17" s="6" t="n">
-        <v>22332</v>
-      </c>
-      <c r="C17" s="6" t="n">
-        <v>20562</v>
-      </c>
-      <c r="D17" s="6" t="n">
-        <v>19678</v>
-      </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="B18" s="7" t="n">
+        <v>6248</v>
+      </c>
+      <c r="C18" s="7" t="n">
+        <v>5142</v>
+      </c>
+      <c r="D18" s="7" t="n">
+        <v>4752</v>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
         <is>
           <t>QSRC=3</t>
         </is>
       </c>
-      <c r="G17" s="6" t="n">
-        <v>21242</v>
-      </c>
-      <c r="H17" s="6" t="n">
-        <v>21972</v>
-      </c>
-      <c r="I17" s="6" t="n">
-        <v>22052</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="G18" s="7" t="n">
+        <v>6092</v>
+      </c>
+      <c r="H18" s="7" t="n">
+        <v>5172</v>
+      </c>
+      <c r="I18" s="7" t="n">
+        <v>4868</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>QSRC=4</t>
         </is>
       </c>
-      <c r="B18" s="6" t="n">
-        <v>22518</v>
-      </c>
-      <c r="C18" s="6" t="n">
-        <v>22738</v>
-      </c>
-      <c r="D18" s="6" t="n">
-        <v>22832</v>
-      </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="B19" s="7" t="n">
+        <v>7012</v>
+      </c>
+      <c r="C19" s="7" t="n">
+        <v>6512</v>
+      </c>
+      <c r="D19" s="7" t="n">
+        <v>6448</v>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
         <is>
           <t>QSRC=4</t>
         </is>
       </c>
-      <c r="G18" s="6" t="n">
-        <v>21998</v>
-      </c>
-      <c r="H18" s="6" t="n">
-        <v>21408</v>
-      </c>
-      <c r="I18" s="6" t="n">
-        <v>21648</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="G19" s="7" t="n">
+        <v>7092</v>
+      </c>
+      <c r="H19" s="7" t="n">
+        <v>6428</v>
+      </c>
+      <c r="I19" s="7" t="n">
+        <v>6412</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>QSRC=5</t>
         </is>
       </c>
-      <c r="B19" s="6" t="n">
-        <v>21998</v>
-      </c>
-      <c r="C19" s="6" t="n">
-        <v>25792</v>
-      </c>
-      <c r="D19" s="6" t="n">
-        <v>24142</v>
-      </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="B20" s="7" t="n">
+        <v>7998</v>
+      </c>
+      <c r="C20" s="7" t="n">
+        <v>7998</v>
+      </c>
+      <c r="D20" s="7" t="n">
+        <v>7908</v>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
         <is>
           <t>QSRC=5</t>
         </is>
       </c>
-      <c r="G19" s="6" t="n">
-        <v>21482</v>
-      </c>
-      <c r="H19" s="6" t="n">
-        <v>23492</v>
-      </c>
-      <c r="I19" s="6" t="n">
-        <v>25498</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>▼ nPedca = 30 / 30        (left block CWds=0   ·   right block CWds=1)</t>
-        </is>
+      <c r="G20" s="7" t="n">
+        <v>8108</v>
+      </c>
+      <c r="H20" s="7" t="n">
+        <v>7912</v>
+      </c>
+      <c r="I20" s="7" t="n">
+        <v>7828</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">   P99</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
           <t>CWds=0</t>
         </is>
       </c>
-      <c r="B22" s="4" t="inlineStr">
+      <c r="B23" s="5" t="inlineStr">
         <is>
           <t>PSRC=1</t>
         </is>
       </c>
-      <c r="C22" s="4" t="inlineStr">
+      <c r="C23" s="5" t="inlineStr">
         <is>
           <t>PSRC=2</t>
         </is>
       </c>
-      <c r="D22" s="4" t="inlineStr">
+      <c r="D23" s="5" t="inlineStr">
         <is>
           <t>PSRC=3</t>
         </is>
       </c>
-      <c r="F22" s="3" t="inlineStr">
+      <c r="F23" s="4" t="inlineStr">
         <is>
           <t>CWds=1</t>
         </is>
       </c>
-      <c r="G22" s="4" t="inlineStr">
+      <c r="G23" s="5" t="inlineStr">
         <is>
           <t>PSRC=1</t>
         </is>
       </c>
-      <c r="H22" s="4" t="inlineStr">
+      <c r="H23" s="5" t="inlineStr">
         <is>
           <t>PSRC=2</t>
         </is>
       </c>
-      <c r="I22" s="4" t="inlineStr">
+      <c r="I23" s="5" t="inlineStr">
         <is>
           <t>PSRC=3</t>
         </is>
       </c>
     </row>
-    <row r="23">
-      <c r="A23" s="5" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>QSRC=0</t>
         </is>
       </c>
-      <c r="B23" s="6" t="n">
-        <v>21072</v>
-      </c>
-      <c r="C23" s="6" t="n">
-        <v>19078</v>
-      </c>
-      <c r="D23" s="6" t="n">
-        <v>13562</v>
-      </c>
-      <c r="F23" s="5" t="inlineStr">
+      <c r="B24" s="7" t="n">
+        <v>12782</v>
+      </c>
+      <c r="C24" s="7" t="n">
+        <v>12518</v>
+      </c>
+      <c r="D24" s="7" t="n">
+        <v>11998</v>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
         <is>
           <t>QSRC=0</t>
         </is>
       </c>
-      <c r="G23" s="6" t="n">
-        <v>21072</v>
-      </c>
-      <c r="H23" s="6" t="n">
-        <v>17998</v>
-      </c>
-      <c r="I23" s="6" t="n">
-        <v>13158</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="5" t="inlineStr">
+      <c r="G24" s="7" t="n">
+        <v>12782</v>
+      </c>
+      <c r="H24" s="7" t="n">
+        <v>11868</v>
+      </c>
+      <c r="I24" s="7" t="n">
+        <v>11222</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
         <is>
           <t>QSRC=1</t>
         </is>
       </c>
-      <c r="B24" s="6" t="n">
-        <v>21722</v>
-      </c>
-      <c r="C24" s="6" t="n">
-        <v>20752</v>
-      </c>
-      <c r="D24" s="6" t="n">
-        <v>11362</v>
-      </c>
-      <c r="F24" s="5" t="inlineStr">
+      <c r="B25" s="7" t="n">
+        <v>12418</v>
+      </c>
+      <c r="C25" s="7" t="n">
+        <v>11618</v>
+      </c>
+      <c r="D25" s="7" t="n">
+        <v>12048</v>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
         <is>
           <t>QSRC=1</t>
         </is>
       </c>
-      <c r="G24" s="6" t="n">
-        <v>22808</v>
-      </c>
-      <c r="H24" s="6" t="n">
-        <v>21298</v>
-      </c>
-      <c r="I24" s="6" t="n">
-        <v>14228</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
+      <c r="G25" s="7" t="n">
+        <v>12582</v>
+      </c>
+      <c r="H25" s="7" t="n">
+        <v>11862</v>
+      </c>
+      <c r="I25" s="7" t="n">
+        <v>10842</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
         <is>
           <t>QSRC=2</t>
         </is>
       </c>
-      <c r="B25" s="6" t="n">
-        <v>24582</v>
-      </c>
-      <c r="C25" s="6" t="n">
-        <v>24712</v>
-      </c>
-      <c r="D25" s="6" t="n">
-        <v>26078</v>
-      </c>
-      <c r="F25" s="5" t="inlineStr">
+      <c r="B26" s="7" t="n">
+        <v>12532</v>
+      </c>
+      <c r="C26" s="7" t="n">
+        <v>11448</v>
+      </c>
+      <c r="D26" s="7" t="n">
+        <v>10858</v>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
         <is>
           <t>QSRC=2</t>
         </is>
       </c>
-      <c r="G25" s="6" t="n">
-        <v>24408</v>
-      </c>
-      <c r="H25" s="6" t="n">
-        <v>25562</v>
-      </c>
-      <c r="I25" s="6" t="n">
-        <v>25648</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="5" t="inlineStr">
+      <c r="G26" s="7" t="n">
+        <v>11978</v>
+      </c>
+      <c r="H26" s="7" t="n">
+        <v>10698</v>
+      </c>
+      <c r="I26" s="7" t="n">
+        <v>9238</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
         <is>
           <t>QSRC=3</t>
         </is>
       </c>
-      <c r="B26" s="6" t="n">
-        <v>23842</v>
-      </c>
-      <c r="C26" s="6" t="n">
-        <v>26892</v>
-      </c>
-      <c r="D26" s="6" t="n">
-        <v>29398</v>
-      </c>
-      <c r="F26" s="5" t="inlineStr">
+      <c r="B27" s="7" t="n">
+        <v>11602</v>
+      </c>
+      <c r="C27" s="7" t="n">
+        <v>10172</v>
+      </c>
+      <c r="D27" s="7" t="n">
+        <v>9338</v>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
         <is>
           <t>QSRC=3</t>
         </is>
       </c>
-      <c r="G26" s="6" t="n">
-        <v>24218</v>
-      </c>
-      <c r="H26" s="6" t="n">
-        <v>27108</v>
-      </c>
-      <c r="I26" s="6" t="n">
-        <v>29812</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="5" t="inlineStr">
+      <c r="G27" s="7" t="n">
+        <v>11608</v>
+      </c>
+      <c r="H27" s="7" t="n">
+        <v>9862</v>
+      </c>
+      <c r="I27" s="7" t="n">
+        <v>8788</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
         <is>
           <t>QSRC=4</t>
         </is>
       </c>
-      <c r="B27" s="6" t="n">
-        <v>23768</v>
-      </c>
-      <c r="C27" s="6" t="n">
-        <v>26618</v>
-      </c>
-      <c r="D27" s="6" t="n">
-        <v>29852</v>
-      </c>
-      <c r="F27" s="5" t="inlineStr">
+      <c r="B28" s="7" t="n">
+        <v>11812</v>
+      </c>
+      <c r="C28" s="7" t="n">
+        <v>10672</v>
+      </c>
+      <c r="D28" s="7" t="n">
+        <v>10108</v>
+      </c>
+      <c r="F28" s="6" t="inlineStr">
         <is>
           <t>QSRC=4</t>
         </is>
       </c>
-      <c r="G27" s="6" t="n">
-        <v>23878</v>
-      </c>
-      <c r="H27" s="6" t="n">
-        <v>26562</v>
-      </c>
-      <c r="I27" s="6" t="n">
-        <v>30412</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
+      <c r="G28" s="7" t="n">
+        <v>11888</v>
+      </c>
+      <c r="H28" s="7" t="n">
+        <v>10262</v>
+      </c>
+      <c r="I28" s="7" t="n">
+        <v>9812</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
         <is>
           <t>QSRC=5</t>
         </is>
       </c>
-      <c r="B28" s="6" t="n">
-        <v>23122</v>
-      </c>
-      <c r="C28" s="6" t="n">
-        <v>26572</v>
-      </c>
-      <c r="D28" s="6" t="n">
-        <v>26472</v>
-      </c>
-      <c r="F28" s="5" t="inlineStr">
+      <c r="B29" s="7" t="n">
+        <v>12222</v>
+      </c>
+      <c r="C29" s="7" t="n">
+        <v>11612</v>
+      </c>
+      <c r="D29" s="7" t="n">
+        <v>11242</v>
+      </c>
+      <c r="F29" s="6" t="inlineStr">
         <is>
           <t>QSRC=5</t>
         </is>
       </c>
-      <c r="G28" s="6" t="n">
-        <v>24412</v>
-      </c>
-      <c r="H28" s="6" t="n">
-        <v>27128</v>
-      </c>
-      <c r="I28" s="6" t="n">
-        <v>28648</v>
+      <c r="G29" s="7" t="n">
+        <v>12038</v>
+      </c>
+      <c r="H29" s="7" t="n">
+        <v>11298</v>
+      </c>
+      <c r="I29" s="7" t="n">
+        <v>11178</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>▼ nPedca = 15 / 30        (left block CWds=0   ·   right block CWds=1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   P50</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>CWds=0</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=1</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=2</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=3</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>CWds=1</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=1</t>
+        </is>
+      </c>
+      <c r="H34" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=2</t>
+        </is>
+      </c>
+      <c r="I34" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=0</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="n">
+        <v>1602</v>
+      </c>
+      <c r="C35" s="7" t="n">
+        <v>1648</v>
+      </c>
+      <c r="D35" s="7" t="n">
+        <v>1688</v>
+      </c>
+      <c r="F35" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=0</t>
+        </is>
+      </c>
+      <c r="G35" s="7" t="n">
+        <v>1602</v>
+      </c>
+      <c r="H35" s="7" t="n">
+        <v>1692</v>
+      </c>
+      <c r="I35" s="7" t="n">
+        <v>1798</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=1</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="n">
+        <v>1768</v>
+      </c>
+      <c r="C36" s="7" t="n">
+        <v>1872</v>
+      </c>
+      <c r="D36" s="7" t="n">
+        <v>1918</v>
+      </c>
+      <c r="F36" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=1</t>
+        </is>
+      </c>
+      <c r="G36" s="7" t="n">
+        <v>1842</v>
+      </c>
+      <c r="H36" s="7" t="n">
+        <v>1978</v>
+      </c>
+      <c r="I36" s="7" t="n">
+        <v>2032</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=2</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="n">
+        <v>1678</v>
+      </c>
+      <c r="C37" s="7" t="n">
+        <v>1612</v>
+      </c>
+      <c r="D37" s="7" t="n">
+        <v>1582</v>
+      </c>
+      <c r="F37" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=2</t>
+        </is>
+      </c>
+      <c r="G37" s="7" t="n">
+        <v>1632</v>
+      </c>
+      <c r="H37" s="7" t="n">
+        <v>1562</v>
+      </c>
+      <c r="I37" s="7" t="n">
+        <v>1532</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=3</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="n">
+        <v>1522</v>
+      </c>
+      <c r="C38" s="7" t="n">
+        <v>1528</v>
+      </c>
+      <c r="D38" s="7" t="n">
+        <v>1552</v>
+      </c>
+      <c r="F38" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=3</t>
+        </is>
+      </c>
+      <c r="G38" s="7" t="n">
+        <v>1498</v>
+      </c>
+      <c r="H38" s="7" t="n">
+        <v>1538</v>
+      </c>
+      <c r="I38" s="7" t="n">
+        <v>1558</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=4</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="n">
+        <v>1768</v>
+      </c>
+      <c r="C39" s="7" t="n">
+        <v>1788</v>
+      </c>
+      <c r="D39" s="7" t="n">
+        <v>1848</v>
+      </c>
+      <c r="F39" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=4</t>
+        </is>
+      </c>
+      <c r="G39" s="7" t="n">
+        <v>1762</v>
+      </c>
+      <c r="H39" s="7" t="n">
+        <v>1782</v>
+      </c>
+      <c r="I39" s="7" t="n">
+        <v>1812</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=5</t>
+        </is>
+      </c>
+      <c r="B40" s="7" t="n">
+        <v>1878</v>
+      </c>
+      <c r="C40" s="7" t="n">
+        <v>1902</v>
+      </c>
+      <c r="D40" s="7" t="n">
+        <v>1892</v>
+      </c>
+      <c r="F40" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=5</t>
+        </is>
+      </c>
+      <c r="G40" s="7" t="n">
+        <v>1852</v>
+      </c>
+      <c r="H40" s="7" t="n">
+        <v>1952</v>
+      </c>
+      <c r="I40" s="7" t="n">
+        <v>1942</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   P95</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>CWds=0</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=1</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=2</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=3</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>CWds=1</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=1</t>
+        </is>
+      </c>
+      <c r="H43" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=2</t>
+        </is>
+      </c>
+      <c r="I43" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=0</t>
+        </is>
+      </c>
+      <c r="B44" s="7" t="n">
+        <v>9342</v>
+      </c>
+      <c r="C44" s="7" t="n">
+        <v>9148</v>
+      </c>
+      <c r="D44" s="7" t="n">
+        <v>9422</v>
+      </c>
+      <c r="F44" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=0</t>
+        </is>
+      </c>
+      <c r="G44" s="7" t="n">
+        <v>9342</v>
+      </c>
+      <c r="H44" s="7" t="n">
+        <v>9002</v>
+      </c>
+      <c r="I44" s="7" t="n">
+        <v>9162</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=1</t>
+        </is>
+      </c>
+      <c r="B45" s="7" t="n">
+        <v>8448</v>
+      </c>
+      <c r="C45" s="7" t="n">
+        <v>8952</v>
+      </c>
+      <c r="D45" s="7" t="n">
+        <v>9082</v>
+      </c>
+      <c r="F45" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=1</t>
+        </is>
+      </c>
+      <c r="G45" s="7" t="n">
+        <v>8998</v>
+      </c>
+      <c r="H45" s="7" t="n">
+        <v>8878</v>
+      </c>
+      <c r="I45" s="7" t="n">
+        <v>8518</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=2</t>
+        </is>
+      </c>
+      <c r="B46" s="7" t="n">
+        <v>8542</v>
+      </c>
+      <c r="C46" s="7" t="n">
+        <v>8182</v>
+      </c>
+      <c r="D46" s="7" t="n">
+        <v>7622</v>
+      </c>
+      <c r="F46" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=2</t>
+        </is>
+      </c>
+      <c r="G46" s="7" t="n">
+        <v>8222</v>
+      </c>
+      <c r="H46" s="7" t="n">
+        <v>7332</v>
+      </c>
+      <c r="I46" s="7" t="n">
+        <v>6948</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=3</t>
+        </is>
+      </c>
+      <c r="B47" s="7" t="n">
+        <v>7648</v>
+      </c>
+      <c r="C47" s="7" t="n">
+        <v>7168</v>
+      </c>
+      <c r="D47" s="7" t="n">
+        <v>7158</v>
+      </c>
+      <c r="F47" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=3</t>
+        </is>
+      </c>
+      <c r="G47" s="7" t="n">
+        <v>7532</v>
+      </c>
+      <c r="H47" s="7" t="n">
+        <v>6828</v>
+      </c>
+      <c r="I47" s="7" t="n">
+        <v>6512</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=4</t>
+        </is>
+      </c>
+      <c r="B48" s="7" t="n">
+        <v>7918</v>
+      </c>
+      <c r="C48" s="7" t="n">
+        <v>7522</v>
+      </c>
+      <c r="D48" s="7" t="n">
+        <v>7822</v>
+      </c>
+      <c r="F48" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=4</t>
+        </is>
+      </c>
+      <c r="G48" s="7" t="n">
+        <v>7738</v>
+      </c>
+      <c r="H48" s="7" t="n">
+        <v>7392</v>
+      </c>
+      <c r="I48" s="7" t="n">
+        <v>7492</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=5</t>
+        </is>
+      </c>
+      <c r="B49" s="7" t="n">
+        <v>8812</v>
+      </c>
+      <c r="C49" s="7" t="n">
+        <v>8912</v>
+      </c>
+      <c r="D49" s="7" t="n">
+        <v>8798</v>
+      </c>
+      <c r="F49" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=5</t>
+        </is>
+      </c>
+      <c r="G49" s="7" t="n">
+        <v>8848</v>
+      </c>
+      <c r="H49" s="7" t="n">
+        <v>9028</v>
+      </c>
+      <c r="I49" s="7" t="n">
+        <v>9082</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   P99</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>CWds=0</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=1</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=2</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=3</t>
+        </is>
+      </c>
+      <c r="F52" s="4" t="inlineStr">
+        <is>
+          <t>CWds=1</t>
+        </is>
+      </c>
+      <c r="G52" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=1</t>
+        </is>
+      </c>
+      <c r="H52" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=2</t>
+        </is>
+      </c>
+      <c r="I52" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=0</t>
+        </is>
+      </c>
+      <c r="B53" s="7" t="n">
+        <v>14842</v>
+      </c>
+      <c r="C53" s="7" t="n">
+        <v>14902</v>
+      </c>
+      <c r="D53" s="7" t="n">
+        <v>14988</v>
+      </c>
+      <c r="F53" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=0</t>
+        </is>
+      </c>
+      <c r="G53" s="7" t="n">
+        <v>14842</v>
+      </c>
+      <c r="H53" s="7" t="n">
+        <v>14942</v>
+      </c>
+      <c r="I53" s="7" t="n">
+        <v>15282</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=1</t>
+        </is>
+      </c>
+      <c r="B54" s="7" t="n">
+        <v>13762</v>
+      </c>
+      <c r="C54" s="7" t="n">
+        <v>14302</v>
+      </c>
+      <c r="D54" s="7" t="n">
+        <v>14518</v>
+      </c>
+      <c r="F54" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=1</t>
+        </is>
+      </c>
+      <c r="G54" s="7" t="n">
+        <v>14198</v>
+      </c>
+      <c r="H54" s="7" t="n">
+        <v>14608</v>
+      </c>
+      <c r="I54" s="7" t="n">
+        <v>14418</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=2</t>
+        </is>
+      </c>
+      <c r="B55" s="7" t="n">
+        <v>13858</v>
+      </c>
+      <c r="C55" s="7" t="n">
+        <v>14022</v>
+      </c>
+      <c r="D55" s="7" t="n">
+        <v>13802</v>
+      </c>
+      <c r="F55" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=2</t>
+        </is>
+      </c>
+      <c r="G55" s="7" t="n">
+        <v>13698</v>
+      </c>
+      <c r="H55" s="7" t="n">
+        <v>13742</v>
+      </c>
+      <c r="I55" s="7" t="n">
+        <v>13862</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=3</t>
+        </is>
+      </c>
+      <c r="B56" s="7" t="n">
+        <v>13318</v>
+      </c>
+      <c r="C56" s="7" t="n">
+        <v>13172</v>
+      </c>
+      <c r="D56" s="7" t="n">
+        <v>13252</v>
+      </c>
+      <c r="F56" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=3</t>
+        </is>
+      </c>
+      <c r="G56" s="7" t="n">
+        <v>13228</v>
+      </c>
+      <c r="H56" s="7" t="n">
+        <v>12968</v>
+      </c>
+      <c r="I56" s="7" t="n">
+        <v>12638</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=4</t>
+        </is>
+      </c>
+      <c r="B57" s="7" t="n">
+        <v>12948</v>
+      </c>
+      <c r="C57" s="7" t="n">
+        <v>12322</v>
+      </c>
+      <c r="D57" s="7" t="n">
+        <v>12698</v>
+      </c>
+      <c r="F57" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=4</t>
+        </is>
+      </c>
+      <c r="G57" s="7" t="n">
+        <v>12792</v>
+      </c>
+      <c r="H57" s="7" t="n">
+        <v>12072</v>
+      </c>
+      <c r="I57" s="7" t="n">
+        <v>11782</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=5</t>
+        </is>
+      </c>
+      <c r="B58" s="7" t="n">
+        <v>13128</v>
+      </c>
+      <c r="C58" s="7" t="n">
+        <v>12998</v>
+      </c>
+      <c r="D58" s="7" t="n">
+        <v>12808</v>
+      </c>
+      <c r="F58" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=5</t>
+        </is>
+      </c>
+      <c r="G58" s="7" t="n">
+        <v>13188</v>
+      </c>
+      <c r="H58" s="7" t="n">
+        <v>13042</v>
+      </c>
+      <c r="I58" s="7" t="n">
+        <v>12978</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>▼ nPedca = 30 / 30        (left block CWds=0   ·   right block CWds=1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   P50</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="4" t="inlineStr">
+        <is>
+          <t>CWds=0</t>
+        </is>
+      </c>
+      <c r="B63" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=1</t>
+        </is>
+      </c>
+      <c r="C63" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=2</t>
+        </is>
+      </c>
+      <c r="D63" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=3</t>
+        </is>
+      </c>
+      <c r="F63" s="4" t="inlineStr">
+        <is>
+          <t>CWds=1</t>
+        </is>
+      </c>
+      <c r="G63" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=1</t>
+        </is>
+      </c>
+      <c r="H63" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=2</t>
+        </is>
+      </c>
+      <c r="I63" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=0</t>
+        </is>
+      </c>
+      <c r="B64" s="7" t="n">
+        <v>1798</v>
+      </c>
+      <c r="C64" s="7" t="n">
+        <v>1838</v>
+      </c>
+      <c r="D64" s="7" t="n">
+        <v>1862</v>
+      </c>
+      <c r="F64" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=0</t>
+        </is>
+      </c>
+      <c r="G64" s="7" t="n">
+        <v>1798</v>
+      </c>
+      <c r="H64" s="7" t="n">
+        <v>1868</v>
+      </c>
+      <c r="I64" s="7" t="n">
+        <v>1962</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=1</t>
+        </is>
+      </c>
+      <c r="B65" s="7" t="n">
+        <v>1922</v>
+      </c>
+      <c r="C65" s="7" t="n">
+        <v>1948</v>
+      </c>
+      <c r="D65" s="7" t="n">
+        <v>2028</v>
+      </c>
+      <c r="F65" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=1</t>
+        </is>
+      </c>
+      <c r="G65" s="7" t="n">
+        <v>1972</v>
+      </c>
+      <c r="H65" s="7" t="n">
+        <v>2092</v>
+      </c>
+      <c r="I65" s="7" t="n">
+        <v>2208</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=2</t>
+        </is>
+      </c>
+      <c r="B66" s="7" t="n">
+        <v>1798</v>
+      </c>
+      <c r="C66" s="7" t="n">
+        <v>1792</v>
+      </c>
+      <c r="D66" s="7" t="n">
+        <v>1778</v>
+      </c>
+      <c r="F66" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=2</t>
+        </is>
+      </c>
+      <c r="G66" s="7" t="n">
+        <v>1802</v>
+      </c>
+      <c r="H66" s="7" t="n">
+        <v>1752</v>
+      </c>
+      <c r="I66" s="7" t="n">
+        <v>1718</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=3</t>
+        </is>
+      </c>
+      <c r="B67" s="7" t="n">
+        <v>1642</v>
+      </c>
+      <c r="C67" s="7" t="n">
+        <v>1698</v>
+      </c>
+      <c r="D67" s="7" t="n">
+        <v>1758</v>
+      </c>
+      <c r="F67" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=3</t>
+        </is>
+      </c>
+      <c r="G67" s="7" t="n">
+        <v>1648</v>
+      </c>
+      <c r="H67" s="7" t="n">
+        <v>1672</v>
+      </c>
+      <c r="I67" s="7" t="n">
+        <v>1762</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=4</t>
+        </is>
+      </c>
+      <c r="B68" s="7" t="n">
+        <v>1862</v>
+      </c>
+      <c r="C68" s="7" t="n">
+        <v>1898</v>
+      </c>
+      <c r="D68" s="7" t="n">
+        <v>1942</v>
+      </c>
+      <c r="F68" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=4</t>
+        </is>
+      </c>
+      <c r="G68" s="7" t="n">
+        <v>1898</v>
+      </c>
+      <c r="H68" s="7" t="n">
+        <v>1978</v>
+      </c>
+      <c r="I68" s="7" t="n">
+        <v>2028</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=5</t>
+        </is>
+      </c>
+      <c r="B69" s="7" t="n">
+        <v>1938</v>
+      </c>
+      <c r="C69" s="7" t="n">
+        <v>2018</v>
+      </c>
+      <c r="D69" s="7" t="n">
+        <v>1982</v>
+      </c>
+      <c r="F69" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=5</t>
+        </is>
+      </c>
+      <c r="G69" s="7" t="n">
+        <v>1892</v>
+      </c>
+      <c r="H69" s="7" t="n">
+        <v>2038</v>
+      </c>
+      <c r="I69" s="7" t="n">
+        <v>2128</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   P95</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>CWds=0</t>
+        </is>
+      </c>
+      <c r="B72" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=1</t>
+        </is>
+      </c>
+      <c r="C72" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=2</t>
+        </is>
+      </c>
+      <c r="D72" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=3</t>
+        </is>
+      </c>
+      <c r="F72" s="4" t="inlineStr">
+        <is>
+          <t>CWds=1</t>
+        </is>
+      </c>
+      <c r="G72" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=1</t>
+        </is>
+      </c>
+      <c r="H72" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=2</t>
+        </is>
+      </c>
+      <c r="I72" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=0</t>
+        </is>
+      </c>
+      <c r="B73" s="7" t="n">
+        <v>10862</v>
+      </c>
+      <c r="C73" s="7" t="n">
+        <v>10922</v>
+      </c>
+      <c r="D73" s="7" t="n">
+        <v>10692</v>
+      </c>
+      <c r="F73" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=0</t>
+        </is>
+      </c>
+      <c r="G73" s="7" t="n">
+        <v>10862</v>
+      </c>
+      <c r="H73" s="7" t="n">
+        <v>10722</v>
+      </c>
+      <c r="I73" s="7" t="n">
+        <v>10912</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=1</t>
+        </is>
+      </c>
+      <c r="B74" s="7" t="n">
+        <v>10298</v>
+      </c>
+      <c r="C74" s="7" t="n">
+        <v>10148</v>
+      </c>
+      <c r="D74" s="7" t="n">
+        <v>10672</v>
+      </c>
+      <c r="F74" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=1</t>
+        </is>
+      </c>
+      <c r="G74" s="7" t="n">
+        <v>10388</v>
+      </c>
+      <c r="H74" s="7" t="n">
+        <v>10622</v>
+      </c>
+      <c r="I74" s="7" t="n">
+        <v>10852</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=2</t>
+        </is>
+      </c>
+      <c r="B75" s="7" t="n">
+        <v>9962</v>
+      </c>
+      <c r="C75" s="7" t="n">
+        <v>10072</v>
+      </c>
+      <c r="D75" s="7" t="n">
+        <v>10042</v>
+      </c>
+      <c r="F75" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=2</t>
+        </is>
+      </c>
+      <c r="G75" s="7" t="n">
+        <v>10052</v>
+      </c>
+      <c r="H75" s="7" t="n">
+        <v>10048</v>
+      </c>
+      <c r="I75" s="7" t="n">
+        <v>10248</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=3</t>
+        </is>
+      </c>
+      <c r="B76" s="7" t="n">
+        <v>9132</v>
+      </c>
+      <c r="C76" s="7" t="n">
+        <v>9522</v>
+      </c>
+      <c r="D76" s="7" t="n">
+        <v>9908</v>
+      </c>
+      <c r="F76" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=3</t>
+        </is>
+      </c>
+      <c r="G76" s="7" t="n">
+        <v>9238</v>
+      </c>
+      <c r="H76" s="7" t="n">
+        <v>8958</v>
+      </c>
+      <c r="I76" s="7" t="n">
+        <v>9208</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=4</t>
+        </is>
+      </c>
+      <c r="B77" s="7" t="n">
+        <v>8948</v>
+      </c>
+      <c r="C77" s="7" t="n">
+        <v>9078</v>
+      </c>
+      <c r="D77" s="7" t="n">
+        <v>9232</v>
+      </c>
+      <c r="F77" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=4</t>
+        </is>
+      </c>
+      <c r="G77" s="7" t="n">
+        <v>9152</v>
+      </c>
+      <c r="H77" s="7" t="n">
+        <v>9248</v>
+      </c>
+      <c r="I77" s="7" t="n">
+        <v>9422</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=5</t>
+        </is>
+      </c>
+      <c r="B78" s="7" t="n">
+        <v>9652</v>
+      </c>
+      <c r="C78" s="7" t="n">
+        <v>9942</v>
+      </c>
+      <c r="D78" s="7" t="n">
+        <v>10058</v>
+      </c>
+      <c r="F78" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=5</t>
+        </is>
+      </c>
+      <c r="G78" s="7" t="n">
+        <v>9478</v>
+      </c>
+      <c r="H78" s="7" t="n">
+        <v>10212</v>
+      </c>
+      <c r="I78" s="7" t="n">
+        <v>10718</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   P99</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="4" t="inlineStr">
+        <is>
+          <t>CWds=0</t>
+        </is>
+      </c>
+      <c r="B81" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=1</t>
+        </is>
+      </c>
+      <c r="C81" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=2</t>
+        </is>
+      </c>
+      <c r="D81" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=3</t>
+        </is>
+      </c>
+      <c r="F81" s="4" t="inlineStr">
+        <is>
+          <t>CWds=1</t>
+        </is>
+      </c>
+      <c r="G81" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=1</t>
+        </is>
+      </c>
+      <c r="H81" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=2</t>
+        </is>
+      </c>
+      <c r="I81" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=0</t>
+        </is>
+      </c>
+      <c r="B82" s="7" t="n">
+        <v>15972</v>
+      </c>
+      <c r="C82" s="7" t="n">
+        <v>16082</v>
+      </c>
+      <c r="D82" s="7" t="n">
+        <v>15928</v>
+      </c>
+      <c r="F82" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=0</t>
+        </is>
+      </c>
+      <c r="G82" s="7" t="n">
+        <v>15972</v>
+      </c>
+      <c r="H82" s="7" t="n">
+        <v>16068</v>
+      </c>
+      <c r="I82" s="7" t="n">
+        <v>16358</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=1</t>
+        </is>
+      </c>
+      <c r="B83" s="7" t="n">
+        <v>15032</v>
+      </c>
+      <c r="C83" s="7" t="n">
+        <v>15098</v>
+      </c>
+      <c r="D83" s="7" t="n">
+        <v>15668</v>
+      </c>
+      <c r="F83" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=1</t>
+        </is>
+      </c>
+      <c r="G83" s="7" t="n">
+        <v>15072</v>
+      </c>
+      <c r="H83" s="7" t="n">
+        <v>15692</v>
+      </c>
+      <c r="I83" s="7" t="n">
+        <v>16078</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=2</t>
+        </is>
+      </c>
+      <c r="B84" s="7" t="n">
+        <v>15052</v>
+      </c>
+      <c r="C84" s="7" t="n">
+        <v>15402</v>
+      </c>
+      <c r="D84" s="7" t="n">
+        <v>15318</v>
+      </c>
+      <c r="F84" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=2</t>
+        </is>
+      </c>
+      <c r="G84" s="7" t="n">
+        <v>15078</v>
+      </c>
+      <c r="H84" s="7" t="n">
+        <v>15618</v>
+      </c>
+      <c r="I84" s="7" t="n">
+        <v>16108</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=3</t>
+        </is>
+      </c>
+      <c r="B85" s="7" t="n">
+        <v>14472</v>
+      </c>
+      <c r="C85" s="7" t="n">
+        <v>15072</v>
+      </c>
+      <c r="D85" s="7" t="n">
+        <v>15492</v>
+      </c>
+      <c r="F85" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=3</t>
+        </is>
+      </c>
+      <c r="G85" s="7" t="n">
+        <v>14612</v>
+      </c>
+      <c r="H85" s="7" t="n">
+        <v>14998</v>
+      </c>
+      <c r="I85" s="7" t="n">
+        <v>15538</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=4</t>
+        </is>
+      </c>
+      <c r="B86" s="7" t="n">
+        <v>14258</v>
+      </c>
+      <c r="C86" s="7" t="n">
+        <v>14468</v>
+      </c>
+      <c r="D86" s="7" t="n">
+        <v>14648</v>
+      </c>
+      <c r="F86" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=4</t>
+        </is>
+      </c>
+      <c r="G86" s="7" t="n">
+        <v>14332</v>
+      </c>
+      <c r="H86" s="7" t="n">
+        <v>14718</v>
+      </c>
+      <c r="I86" s="7" t="n">
+        <v>15008</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=5</t>
+        </is>
+      </c>
+      <c r="B87" s="7" t="n">
+        <v>14162</v>
+      </c>
+      <c r="C87" s="7" t="n">
+        <v>14548</v>
+      </c>
+      <c r="D87" s="7" t="n">
+        <v>14642</v>
+      </c>
+      <c r="F87" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=5</t>
+        </is>
+      </c>
+      <c r="G87" s="7" t="n">
+        <v>14072</v>
+      </c>
+      <c r="H87" s="7" t="n">
+        <v>14792</v>
+      </c>
+      <c r="I87" s="7" t="n">
+        <v>15358</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="13">
+    <mergeCell ref="A33:I33"/>
+    <mergeCell ref="A51:I51"/>
+    <mergeCell ref="A71:I71"/>
+    <mergeCell ref="A42:I42"/>
+    <mergeCell ref="A32:I32"/>
+    <mergeCell ref="A13:I13"/>
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A12:I12"/>
-    <mergeCell ref="A21:I21"/>
+    <mergeCell ref="A80:I80"/>
     <mergeCell ref="A3:I3"/>
+    <mergeCell ref="A61:I61"/>
+    <mergeCell ref="A22:I22"/>
+    <mergeCell ref="A4:I4"/>
+    <mergeCell ref="A62:I62"/>
   </mergeCells>
-  <conditionalFormatting sqref="B5:D10">
+  <conditionalFormatting sqref="B6:D11">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -1793,7 +4964,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G5:I10">
+  <conditionalFormatting sqref="G6:I11">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -1805,7 +4976,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B14:D19">
+  <conditionalFormatting sqref="B15:D20">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -1817,7 +4988,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G14:I19">
+  <conditionalFormatting sqref="G15:I20">
     <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="min"/>
@@ -1829,7 +5000,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B23:D28">
+  <conditionalFormatting sqref="B24:D29">
     <cfRule type="colorScale" priority="5">
       <colorScale>
         <cfvo type="min"/>
@@ -1841,8 +5012,152 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G23:I28">
+  <conditionalFormatting sqref="G24:I29">
     <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="002DA44E"/>
+        <color rgb="00E3B341"/>
+        <color rgb="00F85149"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B35:D40">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="002DA44E"/>
+        <color rgb="00E3B341"/>
+        <color rgb="00F85149"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G35:I40">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="002DA44E"/>
+        <color rgb="00E3B341"/>
+        <color rgb="00F85149"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B44:D49">
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="002DA44E"/>
+        <color rgb="00E3B341"/>
+        <color rgb="00F85149"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G44:I49">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="002DA44E"/>
+        <color rgb="00E3B341"/>
+        <color rgb="00F85149"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B53:D58">
+    <cfRule type="colorScale" priority="11">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="002DA44E"/>
+        <color rgb="00E3B341"/>
+        <color rgb="00F85149"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G53:I58">
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="002DA44E"/>
+        <color rgb="00E3B341"/>
+        <color rgb="00F85149"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B64:D69">
+    <cfRule type="colorScale" priority="13">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="002DA44E"/>
+        <color rgb="00E3B341"/>
+        <color rgb="00F85149"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G64:I69">
+    <cfRule type="colorScale" priority="14">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="002DA44E"/>
+        <color rgb="00E3B341"/>
+        <color rgb="00F85149"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B73:D78">
+    <cfRule type="colorScale" priority="15">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="002DA44E"/>
+        <color rgb="00E3B341"/>
+        <color rgb="00F85149"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G73:I78">
+    <cfRule type="colorScale" priority="16">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="002DA44E"/>
+        <color rgb="00E3B341"/>
+        <color rgb="00F85149"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B82:D87">
+    <cfRule type="colorScale" priority="17">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="002DA44E"/>
+        <color rgb="00E3B341"/>
+        <color rgb="00F85149"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G82:I87">
+    <cfRule type="colorScale" priority="18">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
@@ -1864,7 +5179,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
+  <dimension ref="A1:I58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1881,7 +5196,7 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Legacy STAs — P99 VO delay heatmap (µs)   |   rows = QSRC, cols = PSRC   |   green = lower (better), red = higher</t>
+          <t>Legacy STAs — delay heatmap (µs)   |   rows = QSRC, cols = PSRC   |   green = lower (better), red = higher</t>
         </is>
       </c>
     </row>
@@ -1895,461 +5210,1397 @@
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">   P50</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="4" t="inlineStr">
+        <is>
           <t>CWds=0</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>PSRC=1</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C5" s="5" t="inlineStr">
         <is>
           <t>PSRC=2</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D5" s="5" t="inlineStr">
         <is>
           <t>PSRC=3</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F5" s="4" t="inlineStr">
         <is>
           <t>CWds=1</t>
         </is>
       </c>
-      <c r="G4" s="4" t="inlineStr">
+      <c r="G5" s="5" t="inlineStr">
         <is>
           <t>PSRC=1</t>
         </is>
       </c>
-      <c r="H4" s="4" t="inlineStr">
+      <c r="H5" s="5" t="inlineStr">
         <is>
           <t>PSRC=2</t>
         </is>
       </c>
-      <c r="I4" s="4" t="inlineStr">
+      <c r="I5" s="5" t="inlineStr">
         <is>
           <t>PSRC=3</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>QSRC=0</t>
         </is>
       </c>
-      <c r="B5" s="6" t="n">
-        <v>22412</v>
-      </c>
-      <c r="C5" s="6" t="n">
-        <v>21212</v>
-      </c>
-      <c r="D5" s="6" t="n">
-        <v>21178</v>
-      </c>
-      <c r="F5" s="5" t="inlineStr">
+      <c r="B6" s="7" t="n">
+        <v>1842</v>
+      </c>
+      <c r="C6" s="7" t="n">
+        <v>1958</v>
+      </c>
+      <c r="D6" s="7" t="n">
+        <v>1908</v>
+      </c>
+      <c r="F6" s="6" t="inlineStr">
         <is>
           <t>QSRC=0</t>
         </is>
       </c>
-      <c r="G5" s="6" t="n">
-        <v>22412</v>
-      </c>
-      <c r="H5" s="6" t="n">
-        <v>21248</v>
-      </c>
-      <c r="I5" s="6" t="n">
-        <v>21138</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
+      <c r="G6" s="7" t="n">
+        <v>1842</v>
+      </c>
+      <c r="H6" s="7" t="n">
+        <v>1952</v>
+      </c>
+      <c r="I6" s="7" t="n">
+        <v>1978</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
         <is>
           <t>QSRC=1</t>
         </is>
       </c>
-      <c r="B6" s="6" t="n">
-        <v>22392</v>
-      </c>
-      <c r="C6" s="6" t="n">
-        <v>22388</v>
-      </c>
-      <c r="D6" s="6" t="n">
-        <v>21892</v>
-      </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="B7" s="7" t="n">
+        <v>1848</v>
+      </c>
+      <c r="C7" s="7" t="n">
+        <v>1898</v>
+      </c>
+      <c r="D7" s="7" t="n">
+        <v>1918</v>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
         <is>
           <t>QSRC=1</t>
         </is>
       </c>
-      <c r="G6" s="6" t="n">
-        <v>22502</v>
-      </c>
-      <c r="H6" s="6" t="n">
-        <v>22032</v>
-      </c>
-      <c r="I6" s="6" t="n">
-        <v>21642</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="5" t="inlineStr">
+      <c r="G7" s="7" t="n">
+        <v>1828</v>
+      </c>
+      <c r="H7" s="7" t="n">
+        <v>1872</v>
+      </c>
+      <c r="I7" s="7" t="n">
+        <v>1908</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
         <is>
           <t>QSRC=2</t>
         </is>
       </c>
-      <c r="B7" s="6" t="n">
-        <v>21638</v>
-      </c>
-      <c r="C7" s="6" t="n">
-        <v>22332</v>
-      </c>
-      <c r="D7" s="6" t="n">
-        <v>22082</v>
-      </c>
-      <c r="F7" s="5" t="inlineStr">
+      <c r="B8" s="7" t="n">
+        <v>1818</v>
+      </c>
+      <c r="C8" s="7" t="n">
+        <v>1848</v>
+      </c>
+      <c r="D8" s="7" t="n">
+        <v>1852</v>
+      </c>
+      <c r="F8" s="6" t="inlineStr">
         <is>
           <t>QSRC=2</t>
         </is>
       </c>
-      <c r="G7" s="6" t="n">
-        <v>21982</v>
-      </c>
-      <c r="H7" s="6" t="n">
-        <v>21958</v>
-      </c>
-      <c r="I7" s="6" t="n">
-        <v>22908</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+      <c r="G8" s="7" t="n">
+        <v>1808</v>
+      </c>
+      <c r="H8" s="7" t="n">
+        <v>1838</v>
+      </c>
+      <c r="I8" s="7" t="n">
+        <v>1852</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
         <is>
           <t>QSRC=3</t>
         </is>
       </c>
-      <c r="B8" s="6" t="n">
-        <v>22212</v>
-      </c>
-      <c r="C8" s="6" t="n">
-        <v>22132</v>
-      </c>
-      <c r="D8" s="6" t="n">
-        <v>22392</v>
-      </c>
-      <c r="F8" s="5" t="inlineStr">
+      <c r="B9" s="7" t="n">
+        <v>1812</v>
+      </c>
+      <c r="C9" s="7" t="n">
+        <v>1782</v>
+      </c>
+      <c r="D9" s="7" t="n">
+        <v>1758</v>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
         <is>
           <t>QSRC=3</t>
         </is>
       </c>
-      <c r="G8" s="6" t="n">
-        <v>21722</v>
-      </c>
-      <c r="H8" s="6" t="n">
-        <v>22258</v>
-      </c>
-      <c r="I8" s="6" t="n">
-        <v>20682</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+      <c r="G9" s="7" t="n">
+        <v>1758</v>
+      </c>
+      <c r="H9" s="7" t="n">
+        <v>1802</v>
+      </c>
+      <c r="I9" s="7" t="n">
+        <v>1852</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
         <is>
           <t>QSRC=4</t>
         </is>
       </c>
-      <c r="B9" s="6" t="n">
-        <v>21458</v>
-      </c>
-      <c r="C9" s="6" t="n">
-        <v>21148</v>
-      </c>
-      <c r="D9" s="6" t="n">
-        <v>22872</v>
-      </c>
-      <c r="F9" s="5" t="inlineStr">
+      <c r="B10" s="7" t="n">
+        <v>1782</v>
+      </c>
+      <c r="C10" s="7" t="n">
+        <v>1802</v>
+      </c>
+      <c r="D10" s="7" t="n">
+        <v>1788</v>
+      </c>
+      <c r="F10" s="6" t="inlineStr">
         <is>
           <t>QSRC=4</t>
         </is>
       </c>
-      <c r="G9" s="6" t="n">
-        <v>22388</v>
-      </c>
-      <c r="H9" s="6" t="n">
-        <v>22118</v>
-      </c>
-      <c r="I9" s="6" t="n">
-        <v>23162</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+      <c r="G10" s="7" t="n">
+        <v>1772</v>
+      </c>
+      <c r="H10" s="7" t="n">
+        <v>1782</v>
+      </c>
+      <c r="I10" s="7" t="n">
+        <v>1792</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
         <is>
           <t>QSRC=5</t>
         </is>
       </c>
-      <c r="B10" s="6" t="n">
-        <v>21078</v>
-      </c>
-      <c r="C10" s="6" t="n">
-        <v>21778</v>
-      </c>
-      <c r="D10" s="6" t="n">
-        <v>22522</v>
-      </c>
-      <c r="F10" s="5" t="inlineStr">
+      <c r="B11" s="7" t="n">
+        <v>1788</v>
+      </c>
+      <c r="C11" s="7" t="n">
+        <v>1782</v>
+      </c>
+      <c r="D11" s="7" t="n">
+        <v>1762</v>
+      </c>
+      <c r="F11" s="6" t="inlineStr">
         <is>
           <t>QSRC=5</t>
         </is>
       </c>
-      <c r="G10" s="6" t="n">
-        <v>20158</v>
-      </c>
-      <c r="H10" s="6" t="n">
-        <v>21582</v>
-      </c>
-      <c r="I10" s="6" t="n">
-        <v>21342</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>▼ nPedca = 15 / 30        (left block CWds=0   ·   right block CWds=1)</t>
-        </is>
+      <c r="G11" s="7" t="n">
+        <v>1768</v>
+      </c>
+      <c r="H11" s="7" t="n">
+        <v>1778</v>
+      </c>
+      <c r="I11" s="7" t="n">
+        <v>1762</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">   P95</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
           <t>CWds=0</t>
         </is>
       </c>
-      <c r="B13" s="4" t="inlineStr">
+      <c r="B14" s="5" t="inlineStr">
         <is>
           <t>PSRC=1</t>
         </is>
       </c>
-      <c r="C13" s="4" t="inlineStr">
+      <c r="C14" s="5" t="inlineStr">
         <is>
           <t>PSRC=2</t>
         </is>
       </c>
-      <c r="D13" s="4" t="inlineStr">
+      <c r="D14" s="5" t="inlineStr">
         <is>
           <t>PSRC=3</t>
         </is>
       </c>
-      <c r="F13" s="3" t="inlineStr">
+      <c r="F14" s="4" t="inlineStr">
         <is>
           <t>CWds=1</t>
         </is>
       </c>
-      <c r="G13" s="4" t="inlineStr">
+      <c r="G14" s="5" t="inlineStr">
         <is>
           <t>PSRC=1</t>
         </is>
       </c>
-      <c r="H13" s="4" t="inlineStr">
+      <c r="H14" s="5" t="inlineStr">
         <is>
           <t>PSRC=2</t>
         </is>
       </c>
-      <c r="I13" s="4" t="inlineStr">
+      <c r="I14" s="5" t="inlineStr">
         <is>
           <t>PSRC=3</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="5" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>QSRC=0</t>
         </is>
       </c>
-      <c r="B14" s="6" t="n">
-        <v>22272</v>
-      </c>
-      <c r="C14" s="6" t="n">
-        <v>21462</v>
-      </c>
-      <c r="D14" s="6" t="n">
-        <v>21332</v>
-      </c>
-      <c r="F14" s="5" t="inlineStr">
+      <c r="B15" s="7" t="n">
+        <v>10298</v>
+      </c>
+      <c r="C15" s="7" t="n">
+        <v>10968</v>
+      </c>
+      <c r="D15" s="7" t="n">
+        <v>10728</v>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
         <is>
           <t>QSRC=0</t>
         </is>
       </c>
-      <c r="G14" s="6" t="n">
-        <v>22272</v>
-      </c>
-      <c r="H14" s="6" t="n">
-        <v>22252</v>
-      </c>
-      <c r="I14" s="6" t="n">
-        <v>20888</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="G15" s="7" t="n">
+        <v>10298</v>
+      </c>
+      <c r="H15" s="7" t="n">
+        <v>10992</v>
+      </c>
+      <c r="I15" s="7" t="n">
+        <v>11168</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
         <is>
           <t>QSRC=1</t>
         </is>
       </c>
-      <c r="B15" s="6" t="n">
-        <v>22502</v>
-      </c>
-      <c r="C15" s="6" t="n">
-        <v>22932</v>
-      </c>
-      <c r="D15" s="6" t="n">
-        <v>22072</v>
-      </c>
-      <c r="F15" s="5" t="inlineStr">
+      <c r="B16" s="7" t="n">
+        <v>10278</v>
+      </c>
+      <c r="C16" s="7" t="n">
+        <v>10462</v>
+      </c>
+      <c r="D16" s="7" t="n">
+        <v>10702</v>
+      </c>
+      <c r="F16" s="6" t="inlineStr">
         <is>
           <t>QSRC=1</t>
         </is>
       </c>
-      <c r="G15" s="6" t="n">
-        <v>22592</v>
-      </c>
-      <c r="H15" s="6" t="n">
-        <v>22732</v>
-      </c>
-      <c r="I15" s="6" t="n">
-        <v>22812</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="5" t="inlineStr">
+      <c r="G16" s="7" t="n">
+        <v>10108</v>
+      </c>
+      <c r="H16" s="7" t="n">
+        <v>10452</v>
+      </c>
+      <c r="I16" s="7" t="n">
+        <v>10608</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
         <is>
           <t>QSRC=2</t>
         </is>
       </c>
-      <c r="B16" s="6" t="n">
-        <v>23992</v>
-      </c>
-      <c r="C16" s="6" t="n">
-        <v>22538</v>
-      </c>
-      <c r="D16" s="6" t="n">
-        <v>24218</v>
-      </c>
-      <c r="F16" s="5" t="inlineStr">
+      <c r="B17" s="7" t="n">
+        <v>10082</v>
+      </c>
+      <c r="C17" s="7" t="n">
+        <v>10232</v>
+      </c>
+      <c r="D17" s="7" t="n">
+        <v>10258</v>
+      </c>
+      <c r="F17" s="6" t="inlineStr">
         <is>
           <t>QSRC=2</t>
         </is>
       </c>
-      <c r="G16" s="6" t="n">
-        <v>21712</v>
-      </c>
-      <c r="H16" s="6" t="n">
-        <v>23702</v>
-      </c>
-      <c r="I16" s="6" t="n">
-        <v>24122</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="5" t="inlineStr">
+      <c r="G17" s="7" t="n">
+        <v>9902</v>
+      </c>
+      <c r="H17" s="7" t="n">
+        <v>10208</v>
+      </c>
+      <c r="I17" s="7" t="n">
+        <v>10338</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
         <is>
           <t>QSRC=3</t>
         </is>
       </c>
-      <c r="B17" s="6" t="n">
-        <v>23332</v>
-      </c>
-      <c r="C17" s="6" t="n">
-        <v>22868</v>
-      </c>
-      <c r="D17" s="6" t="n">
-        <v>22358</v>
-      </c>
-      <c r="F17" s="5" t="inlineStr">
+      <c r="B18" s="7" t="n">
+        <v>9948</v>
+      </c>
+      <c r="C18" s="7" t="n">
+        <v>9912</v>
+      </c>
+      <c r="D18" s="7" t="n">
+        <v>9758</v>
+      </c>
+      <c r="F18" s="6" t="inlineStr">
         <is>
           <t>QSRC=3</t>
         </is>
       </c>
-      <c r="G17" s="6" t="n">
-        <v>22812</v>
-      </c>
-      <c r="H17" s="6" t="n">
-        <v>23522</v>
-      </c>
-      <c r="I17" s="6" t="n">
-        <v>23528</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="5" t="inlineStr">
+      <c r="G18" s="7" t="n">
+        <v>9708</v>
+      </c>
+      <c r="H18" s="7" t="n">
+        <v>10062</v>
+      </c>
+      <c r="I18" s="7" t="n">
+        <v>10168</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
         <is>
           <t>QSRC=4</t>
         </is>
       </c>
-      <c r="B18" s="6" t="n">
-        <v>23392</v>
-      </c>
-      <c r="C18" s="6" t="n">
-        <v>22942</v>
-      </c>
-      <c r="D18" s="6" t="n">
-        <v>22908</v>
-      </c>
-      <c r="F18" s="5" t="inlineStr">
+      <c r="B19" s="7" t="n">
+        <v>9742</v>
+      </c>
+      <c r="C19" s="7" t="n">
+        <v>9932</v>
+      </c>
+      <c r="D19" s="7" t="n">
+        <v>9912</v>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
         <is>
           <t>QSRC=4</t>
         </is>
       </c>
-      <c r="G18" s="6" t="n">
-        <v>22752</v>
-      </c>
-      <c r="H18" s="6" t="n">
-        <v>22358</v>
-      </c>
-      <c r="I18" s="6" t="n">
-        <v>23292</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
+      <c r="G19" s="7" t="n">
+        <v>9732</v>
+      </c>
+      <c r="H19" s="7" t="n">
+        <v>9768</v>
+      </c>
+      <c r="I19" s="7" t="n">
+        <v>9982</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
         <is>
           <t>QSRC=5</t>
         </is>
       </c>
-      <c r="B19" s="6" t="n">
-        <v>22918</v>
-      </c>
-      <c r="C19" s="6" t="n">
-        <v>24498</v>
-      </c>
-      <c r="D19" s="6" t="n">
-        <v>22758</v>
-      </c>
-      <c r="F19" s="5" t="inlineStr">
+      <c r="B20" s="7" t="n">
+        <v>9768</v>
+      </c>
+      <c r="C20" s="7" t="n">
+        <v>9832</v>
+      </c>
+      <c r="D20" s="7" t="n">
+        <v>9742</v>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
         <is>
           <t>QSRC=5</t>
         </is>
       </c>
-      <c r="G19" s="6" t="n">
-        <v>22728</v>
-      </c>
-      <c r="H19" s="6" t="n">
-        <v>22662</v>
-      </c>
-      <c r="I19" s="6" t="n">
-        <v>23872</v>
+      <c r="G20" s="7" t="n">
+        <v>9788</v>
+      </c>
+      <c r="H20" s="7" t="n">
+        <v>9842</v>
+      </c>
+      <c r="I20" s="7" t="n">
+        <v>9798</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   P99</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>CWds=0</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=1</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=2</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=3</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>CWds=1</t>
+        </is>
+      </c>
+      <c r="G23" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=1</t>
+        </is>
+      </c>
+      <c r="H23" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=2</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=0</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="n">
+        <v>14792</v>
+      </c>
+      <c r="C24" s="7" t="n">
+        <v>15332</v>
+      </c>
+      <c r="D24" s="7" t="n">
+        <v>15218</v>
+      </c>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=0</t>
+        </is>
+      </c>
+      <c r="G24" s="7" t="n">
+        <v>14792</v>
+      </c>
+      <c r="H24" s="7" t="n">
+        <v>15382</v>
+      </c>
+      <c r="I24" s="7" t="n">
+        <v>15582</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=1</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="n">
+        <v>14452</v>
+      </c>
+      <c r="C25" s="7" t="n">
+        <v>14792</v>
+      </c>
+      <c r="D25" s="7" t="n">
+        <v>15012</v>
+      </c>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=1</t>
+        </is>
+      </c>
+      <c r="G25" s="7" t="n">
+        <v>14422</v>
+      </c>
+      <c r="H25" s="7" t="n">
+        <v>14722</v>
+      </c>
+      <c r="I25" s="7" t="n">
+        <v>15088</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=2</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="n">
+        <v>14292</v>
+      </c>
+      <c r="C26" s="7" t="n">
+        <v>14542</v>
+      </c>
+      <c r="D26" s="7" t="n">
+        <v>14538</v>
+      </c>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=2</t>
+        </is>
+      </c>
+      <c r="G26" s="7" t="n">
+        <v>14168</v>
+      </c>
+      <c r="H26" s="7" t="n">
+        <v>14588</v>
+      </c>
+      <c r="I26" s="7" t="n">
+        <v>14698</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=3</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="n">
+        <v>14242</v>
+      </c>
+      <c r="C27" s="7" t="n">
+        <v>14178</v>
+      </c>
+      <c r="D27" s="7" t="n">
+        <v>14092</v>
+      </c>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=3</t>
+        </is>
+      </c>
+      <c r="G27" s="7" t="n">
+        <v>13932</v>
+      </c>
+      <c r="H27" s="7" t="n">
+        <v>14372</v>
+      </c>
+      <c r="I27" s="7" t="n">
+        <v>14472</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=4</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="n">
+        <v>13998</v>
+      </c>
+      <c r="C28" s="7" t="n">
+        <v>14232</v>
+      </c>
+      <c r="D28" s="7" t="n">
+        <v>14222</v>
+      </c>
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=4</t>
+        </is>
+      </c>
+      <c r="G28" s="7" t="n">
+        <v>13958</v>
+      </c>
+      <c r="H28" s="7" t="n">
+        <v>14108</v>
+      </c>
+      <c r="I28" s="7" t="n">
+        <v>14248</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=5</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="n">
+        <v>14068</v>
+      </c>
+      <c r="C29" s="7" t="n">
+        <v>14158</v>
+      </c>
+      <c r="D29" s="7" t="n">
+        <v>14078</v>
+      </c>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=5</t>
+        </is>
+      </c>
+      <c r="G29" s="7" t="n">
+        <v>14082</v>
+      </c>
+      <c r="H29" s="7" t="n">
+        <v>14128</v>
+      </c>
+      <c r="I29" s="7" t="n">
+        <v>14092</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>▼ nPedca = 15 / 30        (left block CWds=0   ·   right block CWds=1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   P50</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="4" t="inlineStr">
+        <is>
+          <t>CWds=0</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=1</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=2</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=3</t>
+        </is>
+      </c>
+      <c r="F34" s="4" t="inlineStr">
+        <is>
+          <t>CWds=1</t>
+        </is>
+      </c>
+      <c r="G34" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=1</t>
+        </is>
+      </c>
+      <c r="H34" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=2</t>
+        </is>
+      </c>
+      <c r="I34" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=0</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="n">
+        <v>2058</v>
+      </c>
+      <c r="C35" s="7" t="n">
+        <v>2098</v>
+      </c>
+      <c r="D35" s="7" t="n">
+        <v>2178</v>
+      </c>
+      <c r="F35" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=0</t>
+        </is>
+      </c>
+      <c r="G35" s="7" t="n">
+        <v>2058</v>
+      </c>
+      <c r="H35" s="7" t="n">
+        <v>2192</v>
+      </c>
+      <c r="I35" s="7" t="n">
+        <v>2368</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=1</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="n">
+        <v>1948</v>
+      </c>
+      <c r="C36" s="7" t="n">
+        <v>2068</v>
+      </c>
+      <c r="D36" s="7" t="n">
+        <v>2118</v>
+      </c>
+      <c r="F36" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=1</t>
+        </is>
+      </c>
+      <c r="G36" s="7" t="n">
+        <v>2028</v>
+      </c>
+      <c r="H36" s="7" t="n">
+        <v>2212</v>
+      </c>
+      <c r="I36" s="7" t="n">
+        <v>2268</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=2</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="n">
+        <v>2032</v>
+      </c>
+      <c r="C37" s="7" t="n">
+        <v>2028</v>
+      </c>
+      <c r="D37" s="7" t="n">
+        <v>1992</v>
+      </c>
+      <c r="F37" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=2</t>
+        </is>
+      </c>
+      <c r="G37" s="7" t="n">
+        <v>1918</v>
+      </c>
+      <c r="H37" s="7" t="n">
+        <v>1988</v>
+      </c>
+      <c r="I37" s="7" t="n">
+        <v>2102</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=3</t>
+        </is>
+      </c>
+      <c r="B38" s="7" t="n">
+        <v>1858</v>
+      </c>
+      <c r="C38" s="7" t="n">
+        <v>1952</v>
+      </c>
+      <c r="D38" s="7" t="n">
+        <v>1952</v>
+      </c>
+      <c r="F38" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=3</t>
+        </is>
+      </c>
+      <c r="G38" s="7" t="n">
+        <v>1882</v>
+      </c>
+      <c r="H38" s="7" t="n">
+        <v>1942</v>
+      </c>
+      <c r="I38" s="7" t="n">
+        <v>2032</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=4</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="n">
+        <v>1858</v>
+      </c>
+      <c r="C39" s="7" t="n">
+        <v>1918</v>
+      </c>
+      <c r="D39" s="7" t="n">
+        <v>1988</v>
+      </c>
+      <c r="F39" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=4</t>
+        </is>
+      </c>
+      <c r="G39" s="7" t="n">
+        <v>1868</v>
+      </c>
+      <c r="H39" s="7" t="n">
+        <v>1878</v>
+      </c>
+      <c r="I39" s="7" t="n">
+        <v>1918</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=5</t>
+        </is>
+      </c>
+      <c r="B40" s="7" t="n">
+        <v>1878</v>
+      </c>
+      <c r="C40" s="7" t="n">
+        <v>1882</v>
+      </c>
+      <c r="D40" s="7" t="n">
+        <v>1872</v>
+      </c>
+      <c r="F40" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=5</t>
+        </is>
+      </c>
+      <c r="G40" s="7" t="n">
+        <v>1862</v>
+      </c>
+      <c r="H40" s="7" t="n">
+        <v>1892</v>
+      </c>
+      <c r="I40" s="7" t="n">
+        <v>1938</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   P95</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>CWds=0</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=1</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=2</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=3</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>CWds=1</t>
+        </is>
+      </c>
+      <c r="G43" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=1</t>
+        </is>
+      </c>
+      <c r="H43" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=2</t>
+        </is>
+      </c>
+      <c r="I43" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=0</t>
+        </is>
+      </c>
+      <c r="B44" s="7" t="n">
+        <v>11568</v>
+      </c>
+      <c r="C44" s="7" t="n">
+        <v>11872</v>
+      </c>
+      <c r="D44" s="7" t="n">
+        <v>12048</v>
+      </c>
+      <c r="F44" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=0</t>
+        </is>
+      </c>
+      <c r="G44" s="7" t="n">
+        <v>11568</v>
+      </c>
+      <c r="H44" s="7" t="n">
+        <v>12328</v>
+      </c>
+      <c r="I44" s="7" t="n">
+        <v>12932</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=1</t>
+        </is>
+      </c>
+      <c r="B45" s="7" t="n">
+        <v>10682</v>
+      </c>
+      <c r="C45" s="7" t="n">
+        <v>11312</v>
+      </c>
+      <c r="D45" s="7" t="n">
+        <v>11552</v>
+      </c>
+      <c r="F45" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=1</t>
+        </is>
+      </c>
+      <c r="G45" s="7" t="n">
+        <v>11022</v>
+      </c>
+      <c r="H45" s="7" t="n">
+        <v>11992</v>
+      </c>
+      <c r="I45" s="7" t="n">
+        <v>12358</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=2</t>
+        </is>
+      </c>
+      <c r="B46" s="7" t="n">
+        <v>11132</v>
+      </c>
+      <c r="C46" s="7" t="n">
+        <v>11238</v>
+      </c>
+      <c r="D46" s="7" t="n">
+        <v>11202</v>
+      </c>
+      <c r="F46" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=2</t>
+        </is>
+      </c>
+      <c r="G46" s="7" t="n">
+        <v>10702</v>
+      </c>
+      <c r="H46" s="7" t="n">
+        <v>11302</v>
+      </c>
+      <c r="I46" s="7" t="n">
+        <v>11918</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=3</t>
+        </is>
+      </c>
+      <c r="B47" s="7" t="n">
+        <v>10488</v>
+      </c>
+      <c r="C47" s="7" t="n">
+        <v>10902</v>
+      </c>
+      <c r="D47" s="7" t="n">
+        <v>11082</v>
+      </c>
+      <c r="F47" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=3</t>
+        </is>
+      </c>
+      <c r="G47" s="7" t="n">
+        <v>10552</v>
+      </c>
+      <c r="H47" s="7" t="n">
+        <v>11088</v>
+      </c>
+      <c r="I47" s="7" t="n">
+        <v>11492</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=4</t>
+        </is>
+      </c>
+      <c r="B48" s="7" t="n">
+        <v>10422</v>
+      </c>
+      <c r="C48" s="7" t="n">
+        <v>10812</v>
+      </c>
+      <c r="D48" s="7" t="n">
+        <v>11178</v>
+      </c>
+      <c r="F48" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=4</t>
+        </is>
+      </c>
+      <c r="G48" s="7" t="n">
+        <v>10488</v>
+      </c>
+      <c r="H48" s="7" t="n">
+        <v>10792</v>
+      </c>
+      <c r="I48" s="7" t="n">
+        <v>11122</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=5</t>
+        </is>
+      </c>
+      <c r="B49" s="7" t="n">
+        <v>10528</v>
+      </c>
+      <c r="C49" s="7" t="n">
+        <v>10708</v>
+      </c>
+      <c r="D49" s="7" t="n">
+        <v>10608</v>
+      </c>
+      <c r="F49" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=5</t>
+        </is>
+      </c>
+      <c r="G49" s="7" t="n">
+        <v>10348</v>
+      </c>
+      <c r="H49" s="7" t="n">
+        <v>10878</v>
+      </c>
+      <c r="I49" s="7" t="n">
+        <v>11078</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   P99</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>CWds=0</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=1</t>
+        </is>
+      </c>
+      <c r="C52" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=2</t>
+        </is>
+      </c>
+      <c r="D52" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=3</t>
+        </is>
+      </c>
+      <c r="F52" s="4" t="inlineStr">
+        <is>
+          <t>CWds=1</t>
+        </is>
+      </c>
+      <c r="G52" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=1</t>
+        </is>
+      </c>
+      <c r="H52" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=2</t>
+        </is>
+      </c>
+      <c r="I52" s="5" t="inlineStr">
+        <is>
+          <t>PSRC=3</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=0</t>
+        </is>
+      </c>
+      <c r="B53" s="7" t="n">
+        <v>15888</v>
+      </c>
+      <c r="C53" s="7" t="n">
+        <v>16322</v>
+      </c>
+      <c r="D53" s="7" t="n">
+        <v>16558</v>
+      </c>
+      <c r="F53" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=0</t>
+        </is>
+      </c>
+      <c r="G53" s="7" t="n">
+        <v>15888</v>
+      </c>
+      <c r="H53" s="7" t="n">
+        <v>16798</v>
+      </c>
+      <c r="I53" s="7" t="n">
+        <v>17502</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=1</t>
+        </is>
+      </c>
+      <c r="B54" s="7" t="n">
+        <v>15002</v>
+      </c>
+      <c r="C54" s="7" t="n">
+        <v>15678</v>
+      </c>
+      <c r="D54" s="7" t="n">
+        <v>15932</v>
+      </c>
+      <c r="F54" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=1</t>
+        </is>
+      </c>
+      <c r="G54" s="7" t="n">
+        <v>15328</v>
+      </c>
+      <c r="H54" s="7" t="n">
+        <v>16292</v>
+      </c>
+      <c r="I54" s="7" t="n">
+        <v>16708</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=2</t>
+        </is>
+      </c>
+      <c r="B55" s="7" t="n">
+        <v>15352</v>
+      </c>
+      <c r="C55" s="7" t="n">
+        <v>15652</v>
+      </c>
+      <c r="D55" s="7" t="n">
+        <v>15668</v>
+      </c>
+      <c r="F55" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=2</t>
+        </is>
+      </c>
+      <c r="G55" s="7" t="n">
+        <v>15088</v>
+      </c>
+      <c r="H55" s="7" t="n">
+        <v>15832</v>
+      </c>
+      <c r="I55" s="7" t="n">
+        <v>16358</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=3</t>
+        </is>
+      </c>
+      <c r="B56" s="7" t="n">
+        <v>14878</v>
+      </c>
+      <c r="C56" s="7" t="n">
+        <v>15318</v>
+      </c>
+      <c r="D56" s="7" t="n">
+        <v>15598</v>
+      </c>
+      <c r="F56" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=3</t>
+        </is>
+      </c>
+      <c r="G56" s="7" t="n">
+        <v>14912</v>
+      </c>
+      <c r="H56" s="7" t="n">
+        <v>15562</v>
+      </c>
+      <c r="I56" s="7" t="n">
+        <v>15998</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=4</t>
+        </is>
+      </c>
+      <c r="B57" s="7" t="n">
+        <v>14902</v>
+      </c>
+      <c r="C57" s="7" t="n">
+        <v>15208</v>
+      </c>
+      <c r="D57" s="7" t="n">
+        <v>15592</v>
+      </c>
+      <c r="F57" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=4</t>
+        </is>
+      </c>
+      <c r="G57" s="7" t="n">
+        <v>14862</v>
+      </c>
+      <c r="H57" s="7" t="n">
+        <v>15348</v>
+      </c>
+      <c r="I57" s="7" t="n">
+        <v>15782</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=5</t>
+        </is>
+      </c>
+      <c r="B58" s="7" t="n">
+        <v>14952</v>
+      </c>
+      <c r="C58" s="7" t="n">
+        <v>15162</v>
+      </c>
+      <c r="D58" s="7" t="n">
+        <v>15038</v>
+      </c>
+      <c r="F58" s="6" t="inlineStr">
+        <is>
+          <t>QSRC=5</t>
+        </is>
+      </c>
+      <c r="G58" s="7" t="n">
+        <v>14758</v>
+      </c>
+      <c r="H58" s="7" t="n">
+        <v>15372</v>
+      </c>
+      <c r="I58" s="7" t="n">
+        <v>15642</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="9">
+    <mergeCell ref="A33:I33"/>
+    <mergeCell ref="A51:I51"/>
+    <mergeCell ref="A42:I42"/>
+    <mergeCell ref="A32:I32"/>
+    <mergeCell ref="A13:I13"/>
     <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A12:I12"/>
     <mergeCell ref="A3:I3"/>
+    <mergeCell ref="A22:I22"/>
+    <mergeCell ref="A4:I4"/>
   </mergeCells>
-  <conditionalFormatting sqref="B5:D10">
+  <conditionalFormatting sqref="B6:D11">
     <cfRule type="colorScale" priority="1">
       <colorScale>
         <cfvo type="min"/>
@@ -2361,7 +6612,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G5:I10">
+  <conditionalFormatting sqref="G6:I11">
     <cfRule type="colorScale" priority="2">
       <colorScale>
         <cfvo type="min"/>
@@ -2373,7 +6624,7 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B14:D19">
+  <conditionalFormatting sqref="B15:D20">
     <cfRule type="colorScale" priority="3">
       <colorScale>
         <cfvo type="min"/>
@@ -2385,8 +6636,104 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G14:I19">
+  <conditionalFormatting sqref="G15:I20">
     <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="002DA44E"/>
+        <color rgb="00E3B341"/>
+        <color rgb="00F85149"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B24:D29">
+    <cfRule type="colorScale" priority="5">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="002DA44E"/>
+        <color rgb="00E3B341"/>
+        <color rgb="00F85149"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G24:I29">
+    <cfRule type="colorScale" priority="6">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="002DA44E"/>
+        <color rgb="00E3B341"/>
+        <color rgb="00F85149"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B35:D40">
+    <cfRule type="colorScale" priority="7">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="002DA44E"/>
+        <color rgb="00E3B341"/>
+        <color rgb="00F85149"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G35:I40">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="002DA44E"/>
+        <color rgb="00E3B341"/>
+        <color rgb="00F85149"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B44:D49">
+    <cfRule type="colorScale" priority="9">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="002DA44E"/>
+        <color rgb="00E3B341"/>
+        <color rgb="00F85149"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G44:I49">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="002DA44E"/>
+        <color rgb="00E3B341"/>
+        <color rgb="00F85149"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="B53:D58">
+    <cfRule type="colorScale" priority="11">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="002DA44E"/>
+        <color rgb="00E3B341"/>
+        <color rgb="00F85149"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G53:I58">
+    <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="min"/>
         <cfvo type="percentile" val="50"/>
